--- a/data/Cercospora_TIME_description.xlsx
+++ b/data/Cercospora_TIME_description.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lsuagctr-my.sharepoint.com/personal/acerutti_agcenter_lsu_edu/Documents/Documents/GitHub/Cercospora_TIME/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="789" documentId="8_{B521CAD1-B04F-41B4-8C4D-BBC1E172B03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E60484D-D2AF-BB4A-9D8D-D115BAF5CB8E}"/>
+  <xr:revisionPtr revIDLastSave="796" documentId="8_{B521CAD1-B04F-41B4-8C4D-BBC1E172B03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BDB7F26-B3D6-4FBB-A82D-FD3E807375E7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{58E64BEA-56DB-4F46-BCEA-90D1CD645A95}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58E64BEA-56DB-4F46-BCEA-90D1CD645A95}"/>
   </bookViews>
   <sheets>
     <sheet name="TIME" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7324" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7324" uniqueCount="473">
   <si>
     <t>year</t>
   </si>
@@ -1460,6 +1460,9 @@
   <si>
     <t>_CHECK</t>
   </si>
+  <si>
+    <t>Prozio</t>
+  </si>
 </sst>
 </file>
 
@@ -1603,10 +1606,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1927,34 +1926,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23849C3F-791D-4DD0-83AD-DB8372CB8CEE}">
   <dimension ref="A1:X483"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" style="7" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" style="7" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2028,7 +2027,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>2024</v>
       </c>
@@ -2105,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2024</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2024</v>
       </c>
@@ -2259,7 +2258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>2024</v>
       </c>
@@ -2336,7 +2335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2024</v>
       </c>
@@ -2413,7 +2412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>2024</v>
       </c>
@@ -2490,7 +2489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2024</v>
       </c>
@@ -2567,7 +2566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>2024</v>
       </c>
@@ -2644,7 +2643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>2024</v>
       </c>
@@ -2721,7 +2720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>2024</v>
       </c>
@@ -2798,7 +2797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>2024</v>
       </c>
@@ -2875,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>2024</v>
       </c>
@@ -2952,7 +2951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2024</v>
       </c>
@@ -3029,7 +3028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>2024</v>
       </c>
@@ -3106,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>2024</v>
       </c>
@@ -3183,7 +3182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>2024</v>
       </c>
@@ -3260,7 +3259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>2024</v>
       </c>
@@ -3337,7 +3336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>2024</v>
       </c>
@@ -3414,7 +3413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>2024</v>
       </c>
@@ -3491,7 +3490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>2024</v>
       </c>
@@ -3568,7 +3567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>2024</v>
       </c>
@@ -3645,7 +3644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>2024</v>
       </c>
@@ -3722,7 +3721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>2024</v>
       </c>
@@ -3799,7 +3798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>2024</v>
       </c>
@@ -3876,7 +3875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>2024</v>
       </c>
@@ -3953,7 +3952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>2024</v>
       </c>
@@ -4030,7 +4029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>2024</v>
       </c>
@@ -4107,7 +4106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>2024</v>
       </c>
@@ -4184,7 +4183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>2024</v>
       </c>
@@ -4261,7 +4260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>2024</v>
       </c>
@@ -4338,7 +4337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>2024</v>
       </c>
@@ -4415,7 +4414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>2024</v>
       </c>
@@ -4492,7 +4491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>2024</v>
       </c>
@@ -4569,7 +4568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>2024</v>
       </c>
@@ -4646,7 +4645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>2024</v>
       </c>
@@ -4723,7 +4722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>2024</v>
       </c>
@@ -4800,7 +4799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>2024</v>
       </c>
@@ -4877,7 +4876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>2024</v>
       </c>
@@ -4954,7 +4953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>2024</v>
       </c>
@@ -5031,7 +5030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>2024</v>
       </c>
@@ -5108,7 +5107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>2024</v>
       </c>
@@ -5185,7 +5184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>2024</v>
       </c>
@@ -5262,7 +5261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>2024</v>
       </c>
@@ -5339,7 +5338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>2024</v>
       </c>
@@ -5416,7 +5415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>2024</v>
       </c>
@@ -5493,7 +5492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>2024</v>
       </c>
@@ -5570,7 +5569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>2024</v>
       </c>
@@ -5647,7 +5646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>2024</v>
       </c>
@@ -5724,7 +5723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>2024</v>
       </c>
@@ -5799,7 +5798,7 @@
       </c>
       <c r="X50" s="7"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>2024</v>
       </c>
@@ -5874,7 +5873,7 @@
       </c>
       <c r="X51" s="7"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>2024</v>
       </c>
@@ -5949,7 +5948,7 @@
       </c>
       <c r="X52" s="7"/>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>2024</v>
       </c>
@@ -6024,7 +6023,7 @@
       </c>
       <c r="X53" s="7"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>2024</v>
       </c>
@@ -6099,7 +6098,7 @@
       </c>
       <c r="X54" s="7"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>2024</v>
       </c>
@@ -6174,7 +6173,7 @@
       </c>
       <c r="X55" s="7"/>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>2024</v>
       </c>
@@ -6249,7 +6248,7 @@
       </c>
       <c r="X56" s="7"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>2024</v>
       </c>
@@ -6324,7 +6323,7 @@
       </c>
       <c r="X57" s="7"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>2024</v>
       </c>
@@ -6399,7 +6398,7 @@
       </c>
       <c r="X58" s="7"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>2024</v>
       </c>
@@ -6474,7 +6473,7 @@
       </c>
       <c r="X59" s="7"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>2024</v>
       </c>
@@ -6549,7 +6548,7 @@
       </c>
       <c r="X60" s="7"/>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>2024</v>
       </c>
@@ -6624,7 +6623,7 @@
       </c>
       <c r="X61" s="7"/>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>2024</v>
       </c>
@@ -6699,7 +6698,7 @@
       </c>
       <c r="X62" s="7"/>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>2024</v>
       </c>
@@ -6774,7 +6773,7 @@
       </c>
       <c r="X63" s="7"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>2024</v>
       </c>
@@ -6849,7 +6848,7 @@
       </c>
       <c r="X64" s="7"/>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>2024</v>
       </c>
@@ -6924,7 +6923,7 @@
       </c>
       <c r="X65" s="7"/>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>2024</v>
       </c>
@@ -6999,7 +6998,7 @@
       </c>
       <c r="X66" s="7"/>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>2024</v>
       </c>
@@ -7074,7 +7073,7 @@
       </c>
       <c r="X67" s="7"/>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>2024</v>
       </c>
@@ -7146,7 +7145,7 @@
       </c>
       <c r="X68" s="7"/>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>2024</v>
       </c>
@@ -7221,7 +7220,7 @@
       </c>
       <c r="X69" s="7"/>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>2024</v>
       </c>
@@ -7296,7 +7295,7 @@
       </c>
       <c r="X70" s="7"/>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>2024</v>
       </c>
@@ -7371,7 +7370,7 @@
       </c>
       <c r="X71" s="7"/>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>2024</v>
       </c>
@@ -7446,7 +7445,7 @@
       </c>
       <c r="X72" s="7"/>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>2024</v>
       </c>
@@ -7521,7 +7520,7 @@
       </c>
       <c r="X73" s="7"/>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>2024</v>
       </c>
@@ -7596,7 +7595,7 @@
       </c>
       <c r="X74" s="7"/>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>2024</v>
       </c>
@@ -7671,7 +7670,7 @@
       </c>
       <c r="X75" s="7"/>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>2024</v>
       </c>
@@ -7746,7 +7745,7 @@
       </c>
       <c r="X76" s="7"/>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>2024</v>
       </c>
@@ -7821,7 +7820,7 @@
       </c>
       <c r="X77" s="7"/>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>2024</v>
       </c>
@@ -7896,7 +7895,7 @@
       </c>
       <c r="X78" s="7"/>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>2024</v>
       </c>
@@ -7971,7 +7970,7 @@
       </c>
       <c r="X79" s="7"/>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>2024</v>
       </c>
@@ -8046,7 +8045,7 @@
       </c>
       <c r="X80" s="7"/>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>2024</v>
       </c>
@@ -8121,7 +8120,7 @@
       </c>
       <c r="X81" s="7"/>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" s="7">
         <v>2024</v>
       </c>
@@ -8181,7 +8180,7 @@
       </c>
       <c r="X82" s="7"/>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>2024</v>
       </c>
@@ -8256,7 +8255,7 @@
       </c>
       <c r="X83" s="7"/>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
         <v>2024</v>
       </c>
@@ -8331,7 +8330,7 @@
       </c>
       <c r="X84" s="7"/>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>2024</v>
       </c>
@@ -8406,7 +8405,7 @@
       </c>
       <c r="X85" s="7"/>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
         <v>2024</v>
       </c>
@@ -8481,7 +8480,7 @@
       </c>
       <c r="X86" s="7"/>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>2024</v>
       </c>
@@ -8556,7 +8555,7 @@
       </c>
       <c r="X87" s="7"/>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
         <v>2024</v>
       </c>
@@ -8631,7 +8630,7 @@
       </c>
       <c r="X88" s="7"/>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
         <v>2024</v>
       </c>
@@ -8706,7 +8705,7 @@
       </c>
       <c r="X89" s="7"/>
     </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
         <v>2024</v>
       </c>
@@ -8781,7 +8780,7 @@
       </c>
       <c r="X90" s="7"/>
     </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
         <v>2024</v>
       </c>
@@ -8856,7 +8855,7 @@
       </c>
       <c r="X91" s="7"/>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>2024</v>
       </c>
@@ -8931,7 +8930,7 @@
       </c>
       <c r="X92" s="7"/>
     </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
         <v>2024</v>
       </c>
@@ -9006,7 +9005,7 @@
       </c>
       <c r="X93" s="7"/>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
         <v>2024</v>
       </c>
@@ -9081,7 +9080,7 @@
       </c>
       <c r="X94" s="7"/>
     </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
         <v>2024</v>
       </c>
@@ -9156,7 +9155,7 @@
       </c>
       <c r="X95" s="7"/>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
         <v>2024</v>
       </c>
@@ -9231,7 +9230,7 @@
       </c>
       <c r="X96" s="7"/>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
         <v>2024</v>
       </c>
@@ -9306,7 +9305,7 @@
       </c>
       <c r="X97" s="7"/>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
         <v>2024</v>
       </c>
@@ -9381,7 +9380,7 @@
       </c>
       <c r="X98" s="7"/>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
         <v>2024</v>
       </c>
@@ -9456,7 +9455,7 @@
       </c>
       <c r="X99" s="7"/>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
         <v>2024</v>
       </c>
@@ -9531,7 +9530,7 @@
       </c>
       <c r="X100" s="7"/>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" s="7">
         <v>2024</v>
       </c>
@@ -9606,7 +9605,7 @@
       </c>
       <c r="X101" s="7"/>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
         <v>2024</v>
       </c>
@@ -9681,7 +9680,7 @@
       </c>
       <c r="X102" s="7"/>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
         <v>2024</v>
       </c>
@@ -9756,7 +9755,7 @@
       </c>
       <c r="X103" s="7"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
         <v>2024</v>
       </c>
@@ -9831,7 +9830,7 @@
       </c>
       <c r="X104" s="7"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
         <v>2024</v>
       </c>
@@ -9906,7 +9905,7 @@
       </c>
       <c r="X105" s="7"/>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
         <v>2024</v>
       </c>
@@ -9981,7 +9980,7 @@
       </c>
       <c r="X106" s="7"/>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
         <v>2024</v>
       </c>
@@ -10056,7 +10055,7 @@
       </c>
       <c r="X107" s="7"/>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
         <v>2024</v>
       </c>
@@ -10131,7 +10130,7 @@
       </c>
       <c r="X108" s="7"/>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
         <v>2024</v>
       </c>
@@ -10206,7 +10205,7 @@
       </c>
       <c r="X109" s="7"/>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
         <v>2024</v>
       </c>
@@ -10281,7 +10280,7 @@
       </c>
       <c r="X110" s="7"/>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
         <v>2024</v>
       </c>
@@ -10356,7 +10355,7 @@
       </c>
       <c r="X111" s="7"/>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
         <v>2024</v>
       </c>
@@ -10431,7 +10430,7 @@
       </c>
       <c r="X112" s="7"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
         <v>2024</v>
       </c>
@@ -10506,7 +10505,7 @@
       </c>
       <c r="X113" s="7"/>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" s="7">
         <v>2024</v>
       </c>
@@ -10581,7 +10580,7 @@
       </c>
       <c r="X114" s="7"/>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" s="7">
         <v>2024</v>
       </c>
@@ -10656,7 +10655,7 @@
       </c>
       <c r="X115" s="7"/>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" s="7">
         <v>2024</v>
       </c>
@@ -10731,7 +10730,7 @@
       </c>
       <c r="X116" s="7"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" s="7">
         <v>2024</v>
       </c>
@@ -10806,7 +10805,7 @@
       </c>
       <c r="X117" s="7"/>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" s="7">
         <v>2024</v>
       </c>
@@ -10881,7 +10880,7 @@
       </c>
       <c r="X118" s="7"/>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" s="7">
         <v>2024</v>
       </c>
@@ -10956,7 +10955,7 @@
       </c>
       <c r="X119" s="7"/>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" s="7">
         <v>2024</v>
       </c>
@@ -11031,7 +11030,7 @@
       </c>
       <c r="X120" s="7"/>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" s="7">
         <v>2024</v>
       </c>
@@ -11106,7 +11105,7 @@
       </c>
       <c r="X121" s="7"/>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" s="7">
         <v>2024</v>
       </c>
@@ -11181,7 +11180,7 @@
       </c>
       <c r="X122" s="7"/>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" s="7">
         <v>2024</v>
       </c>
@@ -11256,7 +11255,7 @@
       </c>
       <c r="X123" s="7"/>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" s="7">
         <v>2024</v>
       </c>
@@ -11331,7 +11330,7 @@
       </c>
       <c r="X124" s="7"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" s="7">
         <v>2024</v>
       </c>
@@ -11406,7 +11405,7 @@
       </c>
       <c r="X125" s="7"/>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" s="7">
         <v>2024</v>
       </c>
@@ -11481,7 +11480,7 @@
       </c>
       <c r="X126" s="7"/>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" s="7">
         <v>2024</v>
       </c>
@@ -11556,7 +11555,7 @@
       </c>
       <c r="X127" s="7"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" s="7">
         <v>2024</v>
       </c>
@@ -11631,7 +11630,7 @@
       </c>
       <c r="X128" s="7"/>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" s="7">
         <v>2024</v>
       </c>
@@ -11706,7 +11705,7 @@
       </c>
       <c r="X129" s="7"/>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" s="7">
         <v>2024</v>
       </c>
@@ -11781,7 +11780,7 @@
       </c>
       <c r="X130" s="7"/>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" s="7">
         <v>2024</v>
       </c>
@@ -11852,7 +11851,7 @@
       <c r="W131" s="10"/>
       <c r="X131" s="7"/>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" s="7">
         <v>2024</v>
       </c>
@@ -11927,7 +11926,7 @@
       </c>
       <c r="X132" s="7"/>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" s="7">
         <v>2024</v>
       </c>
@@ -12002,7 +12001,7 @@
       </c>
       <c r="X133" s="7"/>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" s="7">
         <v>2024</v>
       </c>
@@ -12077,7 +12076,7 @@
       </c>
       <c r="X134" s="7"/>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" s="7">
         <v>2024</v>
       </c>
@@ -12152,7 +12151,7 @@
       </c>
       <c r="X135" s="7"/>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <v>2024</v>
       </c>
@@ -12227,7 +12226,7 @@
       </c>
       <c r="X136" s="7"/>
     </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" s="7">
         <v>2024</v>
       </c>
@@ -12302,7 +12301,7 @@
       </c>
       <c r="X137" s="7"/>
     </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>2025</v>
       </c>
@@ -12340,7 +12339,7 @@
         <v>252</v>
       </c>
       <c r="M138" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N138" s="9" t="s">
         <v>61</v>
@@ -12379,7 +12378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2025</v>
       </c>
@@ -12456,7 +12455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>2025</v>
       </c>
@@ -12494,7 +12493,7 @@
         <v>252</v>
       </c>
       <c r="M140" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N140" s="9" t="s">
         <v>59</v>
@@ -12533,7 +12532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2025</v>
       </c>
@@ -12610,7 +12609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>2025</v>
       </c>
@@ -12687,7 +12686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2025</v>
       </c>
@@ -12764,7 +12763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>2025</v>
       </c>
@@ -12841,7 +12840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2025</v>
       </c>
@@ -12918,7 +12917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>2025</v>
       </c>
@@ -12995,7 +12994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2025</v>
       </c>
@@ -13033,7 +13032,7 @@
         <v>252</v>
       </c>
       <c r="M147" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N147" s="9" t="s">
         <v>58</v>
@@ -13072,7 +13071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>2025</v>
       </c>
@@ -13149,7 +13148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2025</v>
       </c>
@@ -13226,7 +13225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>2025</v>
       </c>
@@ -13303,7 +13302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2025</v>
       </c>
@@ -13380,7 +13379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>2025</v>
       </c>
@@ -13418,7 +13417,7 @@
         <v>252</v>
       </c>
       <c r="M152" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N152" s="9" t="s">
         <v>60</v>
@@ -13457,7 +13456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2025</v>
       </c>
@@ -13534,7 +13533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>2025</v>
       </c>
@@ -13572,7 +13571,7 @@
         <v>252</v>
       </c>
       <c r="M154" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N154" s="8" t="s">
         <v>470</v>
@@ -13611,7 +13610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2025</v>
       </c>
@@ -13688,7 +13687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>2025</v>
       </c>
@@ -13726,7 +13725,7 @@
         <v>252</v>
       </c>
       <c r="M156" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N156" s="9" t="s">
         <v>62</v>
@@ -13765,7 +13764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2025</v>
       </c>
@@ -13842,7 +13841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>2025</v>
       </c>
@@ -13919,7 +13918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2025</v>
       </c>
@@ -13996,7 +13995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>2025</v>
       </c>
@@ -14073,7 +14072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2025</v>
       </c>
@@ -14111,7 +14110,7 @@
         <v>252</v>
       </c>
       <c r="M161" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N161" s="9" t="s">
         <v>60</v>
@@ -14150,7 +14149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>2025</v>
       </c>
@@ -14188,7 +14187,7 @@
         <v>252</v>
       </c>
       <c r="M162" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N162" s="9" t="s">
         <v>59</v>
@@ -14227,7 +14226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2025</v>
       </c>
@@ -14304,7 +14303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>2025</v>
       </c>
@@ -14381,7 +14380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2025</v>
       </c>
@@ -14458,7 +14457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>2025</v>
       </c>
@@ -14496,7 +14495,7 @@
         <v>252</v>
       </c>
       <c r="M166" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N166" s="9" t="s">
         <v>61</v>
@@ -14535,7 +14534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2025</v>
       </c>
@@ -14573,7 +14572,7 @@
         <v>252</v>
       </c>
       <c r="M167" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N167" s="8" t="s">
         <v>470</v>
@@ -14612,7 +14611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>2025</v>
       </c>
@@ -14689,7 +14688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2025</v>
       </c>
@@ -14766,7 +14765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>2025</v>
       </c>
@@ -14843,7 +14842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2025</v>
       </c>
@@ -14920,7 +14919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>2025</v>
       </c>
@@ -14997,7 +14996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2025</v>
       </c>
@@ -15074,7 +15073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>2025</v>
       </c>
@@ -15112,7 +15111,7 @@
         <v>252</v>
       </c>
       <c r="M174" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N174" s="9" t="s">
         <v>58</v>
@@ -15151,7 +15150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2025</v>
       </c>
@@ -15228,7 +15227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>2025</v>
       </c>
@@ -15305,7 +15304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2025</v>
       </c>
@@ -15382,7 +15381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>2025</v>
       </c>
@@ -15420,7 +15419,7 @@
         <v>252</v>
       </c>
       <c r="M178" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N178" s="9" t="s">
         <v>62</v>
@@ -15459,7 +15458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2025</v>
       </c>
@@ -15536,7 +15535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>2025</v>
       </c>
@@ -15597,11 +15596,11 @@
       </c>
       <c r="T180" s="10">
         <f t="shared" si="10"/>
-        <v>10854.162831344007</v>
+        <v>10854.162831344005</v>
       </c>
       <c r="U180" s="11">
         <f t="shared" si="9"/>
-        <v>9682.571660431764</v>
+        <v>9682.5716604317622</v>
       </c>
       <c r="V180" s="10">
         <v>72.069999999999993</v>
@@ -15613,7 +15612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2025</v>
       </c>
@@ -15690,7 +15689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>2025</v>
       </c>
@@ -15728,7 +15727,7 @@
         <v>252</v>
       </c>
       <c r="M182" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N182" s="8" t="s">
         <v>470</v>
@@ -15767,7 +15766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2025</v>
       </c>
@@ -15844,7 +15843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>2025</v>
       </c>
@@ -15921,7 +15920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2025</v>
       </c>
@@ -15998,7 +15997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>2025</v>
       </c>
@@ -16075,7 +16074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2025</v>
       </c>
@@ -16152,7 +16151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>2025</v>
       </c>
@@ -16190,7 +16189,7 @@
         <v>252</v>
       </c>
       <c r="M188" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N188" s="9" t="s">
         <v>60</v>
@@ -16229,7 +16228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2025</v>
       </c>
@@ -16267,7 +16266,7 @@
         <v>252</v>
       </c>
       <c r="M189" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N189" s="9" t="s">
         <v>61</v>
@@ -16306,7 +16305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>2025</v>
       </c>
@@ -16344,7 +16343,7 @@
         <v>252</v>
       </c>
       <c r="M190" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N190" s="9" t="s">
         <v>59</v>
@@ -16383,7 +16382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2025</v>
       </c>
@@ -16460,7 +16459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>2025</v>
       </c>
@@ -16537,7 +16536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2025</v>
       </c>
@@ -16575,7 +16574,7 @@
         <v>252</v>
       </c>
       <c r="M193" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N193" s="9" t="s">
         <v>58</v>
@@ -16614,7 +16613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>2025</v>
       </c>
@@ -16691,7 +16690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2025</v>
       </c>
@@ -16768,7 +16767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>2025</v>
       </c>
@@ -16845,7 +16844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2025</v>
       </c>
@@ -16922,7 +16921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>2025</v>
       </c>
@@ -16999,7 +16998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2025</v>
       </c>
@@ -17076,7 +17075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>2025</v>
       </c>
@@ -17114,7 +17113,7 @@
         <v>252</v>
       </c>
       <c r="M200" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N200" s="9" t="s">
         <v>62</v>
@@ -17153,7 +17152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
         <v>2025</v>
       </c>
@@ -17230,7 +17229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
         <v>2025</v>
       </c>
@@ -17268,7 +17267,7 @@
         <v>23</v>
       </c>
       <c r="M202" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N202" s="9" t="s">
         <v>59</v>
@@ -17307,7 +17306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
         <v>2025</v>
       </c>
@@ -17384,7 +17383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
         <v>2025</v>
       </c>
@@ -17422,7 +17421,7 @@
         <v>23</v>
       </c>
       <c r="M204" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N204" s="9" t="s">
         <v>59</v>
@@ -17461,7 +17460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
         <v>2025</v>
       </c>
@@ -17538,7 +17537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>2025</v>
       </c>
@@ -17576,7 +17575,7 @@
         <v>23</v>
       </c>
       <c r="M206" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N206" s="8" t="s">
         <v>470</v>
@@ -17615,7 +17614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
         <v>2025</v>
       </c>
@@ -17653,7 +17652,7 @@
         <v>23</v>
       </c>
       <c r="M207" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N207" s="9" t="s">
         <v>62</v>
@@ -17692,7 +17691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
         <v>2025</v>
       </c>
@@ -17769,7 +17768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
         <v>2025</v>
       </c>
@@ -17807,7 +17806,7 @@
         <v>23</v>
       </c>
       <c r="M209" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N209" s="9" t="s">
         <v>59</v>
@@ -17846,7 +17845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>2025</v>
       </c>
@@ -17923,7 +17922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
         <v>2025</v>
       </c>
@@ -17961,7 +17960,7 @@
         <v>23</v>
       </c>
       <c r="M211" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N211" s="9" t="s">
         <v>62</v>
@@ -18000,7 +17999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
         <v>2025</v>
       </c>
@@ -18077,7 +18076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
         <v>2025</v>
       </c>
@@ -18115,7 +18114,7 @@
         <v>23</v>
       </c>
       <c r="M213" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N213" s="9" t="s">
         <v>61</v>
@@ -18154,7 +18153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>2025</v>
       </c>
@@ -18231,7 +18230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
         <v>2025</v>
       </c>
@@ -18269,7 +18268,7 @@
         <v>23</v>
       </c>
       <c r="M215" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N215" s="9" t="s">
         <v>61</v>
@@ -18308,7 +18307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>2025</v>
       </c>
@@ -18346,7 +18345,7 @@
         <v>23</v>
       </c>
       <c r="M216" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N216" s="8" t="s">
         <v>470</v>
@@ -18385,7 +18384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
         <v>2025</v>
       </c>
@@ -18462,7 +18461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>2025</v>
       </c>
@@ -18539,7 +18538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
         <v>2025</v>
       </c>
@@ -18616,7 +18615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
         <v>2025</v>
       </c>
@@ -18693,7 +18692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
         <v>2025</v>
       </c>
@@ -18770,7 +18769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>2025</v>
       </c>
@@ -18847,7 +18846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
         <v>2025</v>
       </c>
@@ -18885,7 +18884,7 @@
         <v>23</v>
       </c>
       <c r="M223" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N223" s="9" t="s">
         <v>60</v>
@@ -18924,7 +18923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>2025</v>
       </c>
@@ -18962,7 +18961,7 @@
         <v>23</v>
       </c>
       <c r="M224" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N224" s="9" t="s">
         <v>58</v>
@@ -19001,7 +19000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
         <v>2025</v>
       </c>
@@ -19078,7 +19077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>2025</v>
       </c>
@@ -19116,7 +19115,7 @@
         <v>23</v>
       </c>
       <c r="M226" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N226" s="9" t="s">
         <v>60</v>
@@ -19155,7 +19154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>2025</v>
       </c>
@@ -19232,7 +19231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>2025</v>
       </c>
@@ -19309,7 +19308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
         <v>2025</v>
       </c>
@@ -19386,7 +19385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
         <v>2025</v>
       </c>
@@ -19424,7 +19423,7 @@
         <v>23</v>
       </c>
       <c r="M230" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N230" s="9" t="s">
         <v>59</v>
@@ -19463,7 +19462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
         <v>2025</v>
       </c>
@@ -19540,7 +19539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>2025</v>
       </c>
@@ -19617,7 +19616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
         <v>2025</v>
       </c>
@@ -19655,7 +19654,7 @@
         <v>23</v>
       </c>
       <c r="M233" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N233" s="9" t="s">
         <v>58</v>
@@ -19694,7 +19693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>2025</v>
       </c>
@@ -19771,7 +19770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
         <v>2025</v>
       </c>
@@ -19809,7 +19808,7 @@
         <v>23</v>
       </c>
       <c r="M235" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N235" s="9" t="s">
         <v>61</v>
@@ -19848,7 +19847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>2025</v>
       </c>
@@ -19925,7 +19924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
         <v>2025</v>
       </c>
@@ -19963,7 +19962,7 @@
         <v>23</v>
       </c>
       <c r="M237" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N237" s="8" t="s">
         <v>470</v>
@@ -20002,7 +20001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>2025</v>
       </c>
@@ -20079,7 +20078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <v>2025</v>
       </c>
@@ -20156,7 +20155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
         <v>2025</v>
       </c>
@@ -20233,7 +20232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
         <v>2025</v>
       </c>
@@ -20310,7 +20309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>2025</v>
       </c>
@@ -20387,7 +20386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A243" s="3">
         <v>2025</v>
       </c>
@@ -20464,7 +20463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>2025</v>
       </c>
@@ -20541,7 +20540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
         <v>2025</v>
       </c>
@@ -20618,7 +20617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>2025</v>
       </c>
@@ -20695,7 +20694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
         <v>2025</v>
       </c>
@@ -20772,7 +20771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
         <v>2025</v>
       </c>
@@ -20849,7 +20848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A249" s="3">
         <v>2025</v>
       </c>
@@ -20887,7 +20886,7 @@
         <v>23</v>
       </c>
       <c r="M249" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N249" s="9" t="s">
         <v>58</v>
@@ -20926,7 +20925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>2025</v>
       </c>
@@ -21003,7 +21002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
         <v>2025</v>
       </c>
@@ -21080,7 +21079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
         <v>2025</v>
       </c>
@@ -21157,7 +21156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A253" s="3">
         <v>2025</v>
       </c>
@@ -21195,7 +21194,7 @@
         <v>23</v>
       </c>
       <c r="M253" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N253" s="9" t="s">
         <v>60</v>
@@ -21234,7 +21233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A254" s="3">
         <v>2025</v>
       </c>
@@ -21311,7 +21310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A255" s="3">
         <v>2025</v>
       </c>
@@ -21388,7 +21387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A256" s="3">
         <v>2025</v>
       </c>
@@ -21465,7 +21464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A257" s="3">
         <v>2025</v>
       </c>
@@ -21542,7 +21541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
         <v>2025</v>
       </c>
@@ -21619,7 +21618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A259" s="3">
         <v>2025</v>
       </c>
@@ -21696,7 +21695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
         <v>2025</v>
       </c>
@@ -21773,7 +21772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A261" s="3">
         <v>2025</v>
       </c>
@@ -21850,7 +21849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>2025</v>
       </c>
@@ -21927,7 +21926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A263" s="3">
         <v>2025</v>
       </c>
@@ -21965,7 +21964,7 @@
         <v>23</v>
       </c>
       <c r="M263" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N263" s="8" t="s">
         <v>470</v>
@@ -22004,7 +22003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
         <v>2025</v>
       </c>
@@ -22081,7 +22080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A265" s="3">
         <v>2025</v>
       </c>
@@ -22158,7 +22157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A266" s="3">
         <v>2025</v>
       </c>
@@ -22235,7 +22234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A267" s="3">
         <v>2025</v>
       </c>
@@ -22312,7 +22311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A268" s="3">
         <v>2025</v>
       </c>
@@ -22389,7 +22388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A269" s="3">
         <v>2025</v>
       </c>
@@ -22427,7 +22426,7 @@
         <v>23</v>
       </c>
       <c r="M269" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N269" s="9" t="s">
         <v>62</v>
@@ -22466,7 +22465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A270" s="3">
         <v>2025</v>
       </c>
@@ -22543,7 +22542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A271" s="3">
         <v>2025</v>
       </c>
@@ -22620,7 +22619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A272" s="3">
         <v>2025</v>
       </c>
@@ -22697,7 +22696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A273" s="3">
         <v>2025</v>
       </c>
@@ -22774,7 +22773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A274" s="3">
         <v>2025</v>
       </c>
@@ -22851,7 +22850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A275" s="3">
         <v>2025</v>
       </c>
@@ -22889,7 +22888,7 @@
         <v>23</v>
       </c>
       <c r="M275" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N275" s="9" t="s">
         <v>60</v>
@@ -22928,7 +22927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A276" s="3">
         <v>2025</v>
       </c>
@@ -22966,7 +22965,7 @@
         <v>23</v>
       </c>
       <c r="M276" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N276" s="9" t="s">
         <v>58</v>
@@ -23005,7 +23004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A277" s="3">
         <v>2025</v>
       </c>
@@ -23082,7 +23081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A278" s="3">
         <v>2025</v>
       </c>
@@ -23159,7 +23158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A279" s="3">
         <v>2025</v>
       </c>
@@ -23236,7 +23235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A280" s="3">
         <v>2025</v>
       </c>
@@ -23313,7 +23312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A281" s="3">
         <v>2025</v>
       </c>
@@ -23390,7 +23389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A282" s="3">
         <v>2025</v>
       </c>
@@ -23467,7 +23466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A283" s="3">
         <v>2025</v>
       </c>
@@ -23505,7 +23504,7 @@
         <v>23</v>
       </c>
       <c r="M283" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N283" s="9" t="s">
         <v>61</v>
@@ -23544,7 +23543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A284" s="3">
         <v>2025</v>
       </c>
@@ -23582,7 +23581,7 @@
         <v>23</v>
       </c>
       <c r="M284" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N284" s="9" t="s">
         <v>62</v>
@@ -23621,7 +23620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A285" s="3">
         <v>2025</v>
       </c>
@@ -23698,7 +23697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A286" s="3">
         <v>2025</v>
       </c>
@@ -23775,7 +23774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A287" s="3">
         <v>2025</v>
       </c>
@@ -23813,7 +23812,7 @@
         <v>252</v>
       </c>
       <c r="M287" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N287" s="9" t="s">
         <v>58</v>
@@ -23852,7 +23851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A288" s="3">
         <v>2025</v>
       </c>
@@ -23890,7 +23889,7 @@
         <v>252</v>
       </c>
       <c r="M288" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N288" s="9" t="s">
         <v>59</v>
@@ -23929,7 +23928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="289" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A289" s="3">
         <v>2025</v>
       </c>
@@ -24006,7 +24005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A290" s="3">
         <v>2025</v>
       </c>
@@ -24083,7 +24082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="291" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A291" s="3">
         <v>2025</v>
       </c>
@@ -24121,7 +24120,7 @@
         <v>252</v>
       </c>
       <c r="M291" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N291" s="9" t="s">
         <v>60</v>
@@ -24160,7 +24159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A292" s="3">
         <v>2025</v>
       </c>
@@ -24198,7 +24197,7 @@
         <v>252</v>
       </c>
       <c r="M292" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N292" s="9" t="s">
         <v>62</v>
@@ -24237,7 +24236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A293" s="3">
         <v>2025</v>
       </c>
@@ -24314,7 +24313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A294" s="3">
         <v>2025</v>
       </c>
@@ -24352,7 +24351,7 @@
         <v>252</v>
       </c>
       <c r="M294" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N294" s="9" t="s">
         <v>61</v>
@@ -24391,7 +24390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A295" s="3">
         <v>2025</v>
       </c>
@@ -24468,7 +24467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A296" s="3">
         <v>2025</v>
       </c>
@@ -24506,7 +24505,7 @@
         <v>252</v>
       </c>
       <c r="M296" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N296" s="9" t="s">
         <v>62</v>
@@ -24545,7 +24544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A297" s="3">
         <v>2025</v>
       </c>
@@ -24622,7 +24621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="298" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A298" s="3">
         <v>2025</v>
       </c>
@@ -24699,7 +24698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A299" s="3">
         <v>2025</v>
       </c>
@@ -24776,7 +24775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A300" s="3">
         <v>2025</v>
       </c>
@@ -24853,7 +24852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A301" s="3">
         <v>2025</v>
       </c>
@@ -24891,7 +24890,7 @@
         <v>252</v>
       </c>
       <c r="M301" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N301" s="9" t="s">
         <v>59</v>
@@ -24930,7 +24929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A302" s="3">
         <v>2025</v>
       </c>
@@ -24968,7 +24967,7 @@
         <v>252</v>
       </c>
       <c r="M302" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N302" s="9" t="s">
         <v>60</v>
@@ -25007,7 +25006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A303" s="3">
         <v>2025</v>
       </c>
@@ -25084,7 +25083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A304" s="3">
         <v>2025</v>
       </c>
@@ -25161,7 +25160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A305" s="3">
         <v>2025</v>
       </c>
@@ -25238,7 +25237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A306" s="3">
         <v>2025</v>
       </c>
@@ -25276,7 +25275,7 @@
         <v>252</v>
       </c>
       <c r="M306" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N306" s="9" t="s">
         <v>58</v>
@@ -25315,7 +25314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A307" s="3">
         <v>2025</v>
       </c>
@@ -25353,7 +25352,7 @@
         <v>252</v>
       </c>
       <c r="M307" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N307" s="9" t="s">
         <v>59</v>
@@ -25392,7 +25391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A308" s="3">
         <v>2025</v>
       </c>
@@ -25469,7 +25468,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A309" s="3">
         <v>2025</v>
       </c>
@@ -25546,7 +25545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
         <v>2025</v>
       </c>
@@ -25623,7 +25622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A311" s="3">
         <v>2025</v>
       </c>
@@ -25661,7 +25660,7 @@
         <v>252</v>
       </c>
       <c r="M311" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N311" s="9" t="s">
         <v>58</v>
@@ -25700,7 +25699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A312" s="3">
         <v>2025</v>
       </c>
@@ -25777,7 +25776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A313" s="3">
         <v>2025</v>
       </c>
@@ -25815,7 +25814,7 @@
         <v>252</v>
       </c>
       <c r="M313" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N313" s="8" t="s">
         <v>470</v>
@@ -25854,7 +25853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A314" s="3">
         <v>2025</v>
       </c>
@@ -25931,7 +25930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A315" s="3">
         <v>2025</v>
       </c>
@@ -26008,7 +26007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A316" s="3">
         <v>2025</v>
       </c>
@@ -26085,7 +26084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A317" s="3">
         <v>2025</v>
       </c>
@@ -26162,7 +26161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A318" s="3">
         <v>2025</v>
       </c>
@@ -26239,7 +26238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A319" s="3">
         <v>2025</v>
       </c>
@@ -26277,7 +26276,7 @@
         <v>252</v>
       </c>
       <c r="M319" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N319" s="8" t="s">
         <v>470</v>
@@ -26316,7 +26315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A320" s="3">
         <v>2025</v>
       </c>
@@ -26393,7 +26392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A321" s="3">
         <v>2025</v>
       </c>
@@ -26431,7 +26430,7 @@
         <v>252</v>
       </c>
       <c r="M321" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N321" s="9" t="s">
         <v>60</v>
@@ -26470,7 +26469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
         <v>2025</v>
       </c>
@@ -26547,7 +26546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A323" s="3">
         <v>2025</v>
       </c>
@@ -26585,7 +26584,7 @@
         <v>252</v>
       </c>
       <c r="M323" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N323" s="9" t="s">
         <v>62</v>
@@ -26624,7 +26623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A324" s="3">
         <v>2025</v>
       </c>
@@ -26701,7 +26700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A325" s="3">
         <v>2025</v>
       </c>
@@ -26778,7 +26777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A326" s="3">
         <v>2025</v>
       </c>
@@ -26855,7 +26854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A327" s="3">
         <v>2025</v>
       </c>
@@ -26932,7 +26931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A328" s="3">
         <v>2025</v>
       </c>
@@ -27009,7 +27008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A329" s="3">
         <v>2025</v>
       </c>
@@ -27086,7 +27085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A330" s="3">
         <v>2025</v>
       </c>
@@ -27163,7 +27162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A331" s="3">
         <v>2025</v>
       </c>
@@ -27240,7 +27239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A332" s="3">
         <v>2025</v>
       </c>
@@ -27317,7 +27316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="333" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A333" s="3">
         <v>2025</v>
       </c>
@@ -27355,7 +27354,7 @@
         <v>252</v>
       </c>
       <c r="M333" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N333" s="9" t="s">
         <v>61</v>
@@ -27394,7 +27393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A334" s="3">
         <v>2025</v>
       </c>
@@ -27432,7 +27431,7 @@
         <v>252</v>
       </c>
       <c r="M334" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N334" s="9" t="s">
         <v>61</v>
@@ -27471,7 +27470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A335" s="3">
         <v>2025</v>
       </c>
@@ -27548,7 +27547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A336" s="3">
         <v>2025</v>
       </c>
@@ -27625,7 +27624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A337" s="3">
         <v>2025</v>
       </c>
@@ -27702,7 +27701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="338" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A338" s="3">
         <v>2025</v>
       </c>
@@ -27779,7 +27778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A339" s="3">
         <v>2025</v>
       </c>
@@ -27856,7 +27855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A340" s="3">
         <v>2025</v>
       </c>
@@ -27933,7 +27932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A341" s="3">
         <v>2025</v>
       </c>
@@ -27971,7 +27970,7 @@
         <v>252</v>
       </c>
       <c r="M341" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N341" s="8" t="s">
         <v>470</v>
@@ -28010,7 +28009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A342" s="3">
         <v>2025</v>
       </c>
@@ -28087,7 +28086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="343" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A343" s="3">
         <v>2025</v>
       </c>
@@ -28164,7 +28163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A344" s="3">
         <v>2025</v>
       </c>
@@ -28241,7 +28240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A345" s="3">
         <v>2025</v>
       </c>
@@ -28318,7 +28317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A346" s="3">
         <v>2025</v>
       </c>
@@ -28395,7 +28394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A347" s="3">
         <v>2025</v>
       </c>
@@ -28472,7 +28471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A348" s="3">
         <v>2025</v>
       </c>
@@ -28549,7 +28548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A349" s="3">
         <v>2025</v>
       </c>
@@ -28587,7 +28586,7 @@
         <v>252</v>
       </c>
       <c r="M349" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N349" s="9" t="s">
         <v>60</v>
@@ -28626,7 +28625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A350" s="3">
         <v>2025</v>
       </c>
@@ -28703,7 +28702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A351" s="3">
         <v>2025</v>
       </c>
@@ -28741,7 +28740,7 @@
         <v>252</v>
       </c>
       <c r="M351" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N351" s="9" t="s">
         <v>58</v>
@@ -28780,7 +28779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A352" s="3">
         <v>2025</v>
       </c>
@@ -28857,7 +28856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A353" s="3">
         <v>2025</v>
       </c>
@@ -28934,7 +28933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A354" s="3">
         <v>2025</v>
       </c>
@@ -28972,7 +28971,7 @@
         <v>252</v>
       </c>
       <c r="M354" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N354" s="8" t="s">
         <v>470</v>
@@ -29011,7 +29010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A355" s="3">
         <v>2025</v>
       </c>
@@ -29088,7 +29087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A356" s="3">
         <v>2025</v>
       </c>
@@ -29126,7 +29125,7 @@
         <v>252</v>
       </c>
       <c r="M356" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N356" s="9" t="s">
         <v>62</v>
@@ -29165,7 +29164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A357" s="3">
         <v>2025</v>
       </c>
@@ -29203,7 +29202,7 @@
         <v>252</v>
       </c>
       <c r="M357" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N357" s="9" t="s">
         <v>62</v>
@@ -29242,7 +29241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A358" s="3">
         <v>2025</v>
       </c>
@@ -29319,7 +29318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A359" s="3">
         <v>2025</v>
       </c>
@@ -29396,7 +29395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A360" s="3">
         <v>2025</v>
       </c>
@@ -29434,7 +29433,7 @@
         <v>252</v>
       </c>
       <c r="M360" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N360" s="9" t="s">
         <v>60</v>
@@ -29473,7 +29472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A361" s="3">
         <v>2025</v>
       </c>
@@ -29550,7 +29549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A362" s="3">
         <v>2025</v>
       </c>
@@ -29627,7 +29626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A363" s="3">
         <v>2025</v>
       </c>
@@ -29704,7 +29703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A364" s="3">
         <v>2025</v>
       </c>
@@ -29781,7 +29780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A365" s="3">
         <v>2025</v>
       </c>
@@ -29858,7 +29857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A366" s="3">
         <v>2025</v>
       </c>
@@ -29935,7 +29934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A367" s="3">
         <v>2025</v>
       </c>
@@ -30012,7 +30011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="368" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A368" s="3">
         <v>2025</v>
       </c>
@@ -30089,7 +30088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A369" s="3">
         <v>2025</v>
       </c>
@@ -30166,7 +30165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A370" s="3">
         <v>2025</v>
       </c>
@@ -30204,7 +30203,7 @@
         <v>252</v>
       </c>
       <c r="M370" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N370" s="9" t="s">
         <v>60</v>
@@ -30243,7 +30242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A371" s="3">
         <v>2025</v>
       </c>
@@ -30320,7 +30319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A372" s="3">
         <v>2025</v>
       </c>
@@ -30397,7 +30396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A373" s="3">
         <v>2025</v>
       </c>
@@ -30474,7 +30473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A374" s="3">
         <v>2025</v>
       </c>
@@ -30512,7 +30511,7 @@
         <v>252</v>
       </c>
       <c r="M374" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N374" s="9" t="s">
         <v>58</v>
@@ -30551,7 +30550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A375" s="3">
         <v>2025</v>
       </c>
@@ -30628,7 +30627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A376" s="3">
         <v>2025</v>
       </c>
@@ -30705,7 +30704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A377" s="3">
         <v>2025</v>
       </c>
@@ -30782,7 +30781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A378" s="3">
         <v>2025</v>
       </c>
@@ -30820,7 +30819,7 @@
         <v>252</v>
       </c>
       <c r="M378" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N378" s="9" t="s">
         <v>59</v>
@@ -30859,7 +30858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A379" s="3">
         <v>2025</v>
       </c>
@@ -30936,7 +30935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A380" s="3">
         <v>2025</v>
       </c>
@@ -31013,7 +31012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A381" s="3">
         <v>2025</v>
       </c>
@@ -31051,7 +31050,7 @@
         <v>252</v>
       </c>
       <c r="M381" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N381" s="9" t="s">
         <v>59</v>
@@ -31090,7 +31089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A382" s="3">
         <v>2025</v>
       </c>
@@ -31167,7 +31166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A383" s="3">
         <v>2025</v>
       </c>
@@ -31244,7 +31243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A384" s="3">
         <v>2025</v>
       </c>
@@ -31321,7 +31320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A385" s="3">
         <v>2025</v>
       </c>
@@ -31398,7 +31397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A386" s="3">
         <v>2025</v>
       </c>
@@ -31475,7 +31474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A387" s="3">
         <v>2025</v>
       </c>
@@ -31552,7 +31551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A388" s="3">
         <v>2025</v>
       </c>
@@ -31629,7 +31628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A389" s="3">
         <v>2025</v>
       </c>
@@ -31706,7 +31705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A390" s="3">
         <v>2025</v>
       </c>
@@ -31783,7 +31782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A391" s="3">
         <v>2025</v>
       </c>
@@ -31860,7 +31859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A392" s="3">
         <v>2025</v>
       </c>
@@ -31937,7 +31936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A393" s="3">
         <v>2025</v>
       </c>
@@ -31975,7 +31974,7 @@
         <v>252</v>
       </c>
       <c r="M393" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N393" s="9" t="s">
         <v>61</v>
@@ -32014,7 +32013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A394" s="3">
         <v>2025</v>
       </c>
@@ -32052,7 +32051,7 @@
         <v>252</v>
       </c>
       <c r="M394" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N394" s="8" t="s">
         <v>470</v>
@@ -32091,7 +32090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A395" s="3">
         <v>2025</v>
       </c>
@@ -32129,7 +32128,7 @@
         <v>252</v>
       </c>
       <c r="M395" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N395" s="9" t="s">
         <v>61</v>
@@ -32168,7 +32167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A396" s="3">
         <v>2025</v>
       </c>
@@ -32206,7 +32205,7 @@
         <v>252</v>
       </c>
       <c r="M396" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N396" s="9" t="s">
         <v>62</v>
@@ -32245,7 +32244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A397" s="3">
         <v>2025</v>
       </c>
@@ -32283,7 +32282,7 @@
         <v>252</v>
       </c>
       <c r="M397" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N397" s="8" t="s">
         <v>470</v>
@@ -32322,7 +32321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A398" s="3">
         <v>2025</v>
       </c>
@@ -32399,7 +32398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A399" s="3">
         <v>2025</v>
       </c>
@@ -32476,7 +32475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A400" s="3">
         <v>2025</v>
       </c>
@@ -32553,7 +32552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A401" s="3">
         <v>2025</v>
       </c>
@@ -32591,7 +32590,7 @@
         <v>252</v>
       </c>
       <c r="M401" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N401" s="9" t="s">
         <v>58</v>
@@ -32630,7 +32629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A402" s="3">
         <v>2025</v>
       </c>
@@ -32707,7 +32706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="403" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A403" s="3">
         <v>2025</v>
       </c>
@@ -32745,7 +32744,7 @@
         <v>252</v>
       </c>
       <c r="M403" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N403" s="9" t="s">
         <v>59</v>
@@ -32784,7 +32783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A404" s="3">
         <v>2025</v>
       </c>
@@ -32822,7 +32821,7 @@
         <v>252</v>
       </c>
       <c r="M404" s="8" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="N404" s="9" t="s">
         <v>61</v>
@@ -32861,7 +32860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A405" s="6"/>
       <c r="B405" s="6"/>
       <c r="C405" s="6"/>
@@ -32885,7 +32884,7 @@
       <c r="U405" s="6"/>
       <c r="V405" s="6"/>
     </row>
-    <row r="406" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A406" s="6"/>
       <c r="B406" s="6"/>
       <c r="C406" s="6"/>
@@ -32909,7 +32908,7 @@
       <c r="U406" s="6"/>
       <c r="V406" s="6"/>
     </row>
-    <row r="407" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A407" s="6"/>
       <c r="B407" s="6"/>
       <c r="C407" s="6"/>
@@ -32933,7 +32932,7 @@
       <c r="U407" s="6"/>
       <c r="V407" s="6"/>
     </row>
-    <row r="408" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A408" s="6"/>
       <c r="B408" s="6"/>
       <c r="C408" s="6"/>
@@ -32957,7 +32956,7 @@
       <c r="U408" s="6"/>
       <c r="V408" s="6"/>
     </row>
-    <row r="409" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A409" s="6"/>
       <c r="B409" s="6"/>
       <c r="C409" s="6"/>
@@ -32981,7 +32980,7 @@
       <c r="U409" s="6"/>
       <c r="V409" s="6"/>
     </row>
-    <row r="410" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A410" s="6"/>
       <c r="B410" s="6"/>
       <c r="C410" s="6"/>
@@ -33005,7 +33004,7 @@
       <c r="U410" s="6"/>
       <c r="V410" s="6"/>
     </row>
-    <row r="411" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A411" s="6"/>
       <c r="B411" s="6"/>
       <c r="C411" s="6"/>
@@ -33029,7 +33028,7 @@
       <c r="U411" s="6"/>
       <c r="V411" s="6"/>
     </row>
-    <row r="412" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A412" s="6"/>
       <c r="B412" s="6"/>
       <c r="C412" s="6"/>
@@ -33053,7 +33052,7 @@
       <c r="U412" s="6"/>
       <c r="V412" s="6"/>
     </row>
-    <row r="413" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A413" s="6"/>
       <c r="B413" s="6"/>
       <c r="C413" s="6"/>
@@ -33077,7 +33076,7 @@
       <c r="U413" s="6"/>
       <c r="V413" s="6"/>
     </row>
-    <row r="414" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A414" s="6"/>
       <c r="B414" s="6"/>
       <c r="C414" s="6"/>
@@ -33101,7 +33100,7 @@
       <c r="U414" s="6"/>
       <c r="V414" s="6"/>
     </row>
-    <row r="415" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A415" s="6"/>
       <c r="B415" s="6"/>
       <c r="C415" s="6"/>
@@ -33125,7 +33124,7 @@
       <c r="U415" s="6"/>
       <c r="V415" s="6"/>
     </row>
-    <row r="416" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A416" s="6"/>
       <c r="B416" s="6"/>
       <c r="C416" s="6"/>
@@ -33149,7 +33148,7 @@
       <c r="U416" s="6"/>
       <c r="V416" s="6"/>
     </row>
-    <row r="417" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A417" s="6"/>
       <c r="B417" s="6"/>
       <c r="C417" s="6"/>
@@ -33173,7 +33172,7 @@
       <c r="U417" s="6"/>
       <c r="V417" s="6"/>
     </row>
-    <row r="418" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A418" s="6"/>
       <c r="B418" s="6"/>
       <c r="C418" s="6"/>
@@ -33197,7 +33196,7 @@
       <c r="U418" s="6"/>
       <c r="V418" s="6"/>
     </row>
-    <row r="419" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A419" s="6"/>
       <c r="B419" s="6"/>
       <c r="C419" s="6"/>
@@ -33221,7 +33220,7 @@
       <c r="U419" s="6"/>
       <c r="V419" s="6"/>
     </row>
-    <row r="420" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A420" s="6"/>
       <c r="B420" s="6"/>
       <c r="C420" s="6"/>
@@ -33245,7 +33244,7 @@
       <c r="U420" s="6"/>
       <c r="V420" s="6"/>
     </row>
-    <row r="421" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A421" s="6"/>
       <c r="B421" s="6"/>
       <c r="C421" s="6"/>
@@ -33269,7 +33268,7 @@
       <c r="U421" s="6"/>
       <c r="V421" s="6"/>
     </row>
-    <row r="422" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A422" s="6"/>
       <c r="B422" s="6"/>
       <c r="C422" s="6"/>
@@ -33293,7 +33292,7 @@
       <c r="U422" s="6"/>
       <c r="V422" s="6"/>
     </row>
-    <row r="423" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A423" s="6"/>
       <c r="B423" s="6"/>
       <c r="C423" s="6"/>
@@ -33317,7 +33316,7 @@
       <c r="U423" s="6"/>
       <c r="V423" s="6"/>
     </row>
-    <row r="424" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A424" s="6"/>
       <c r="B424" s="6"/>
       <c r="C424" s="6"/>
@@ -33341,7 +33340,7 @@
       <c r="U424" s="6"/>
       <c r="V424" s="6"/>
     </row>
-    <row r="425" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A425" s="6"/>
       <c r="B425" s="6"/>
       <c r="C425" s="6"/>
@@ -33365,7 +33364,7 @@
       <c r="U425" s="6"/>
       <c r="V425" s="6"/>
     </row>
-    <row r="426" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A426" s="6"/>
       <c r="B426" s="6"/>
       <c r="C426" s="6"/>
@@ -33389,7 +33388,7 @@
       <c r="U426" s="6"/>
       <c r="V426" s="6"/>
     </row>
-    <row r="427" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A427" s="6"/>
       <c r="B427" s="6"/>
       <c r="C427" s="6"/>
@@ -33413,7 +33412,7 @@
       <c r="U427" s="6"/>
       <c r="V427" s="6"/>
     </row>
-    <row r="428" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A428" s="6"/>
       <c r="B428" s="6"/>
       <c r="C428" s="6"/>
@@ -33437,7 +33436,7 @@
       <c r="U428" s="6"/>
       <c r="V428" s="6"/>
     </row>
-    <row r="429" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A429" s="6"/>
       <c r="B429" s="6"/>
       <c r="C429" s="6"/>
@@ -33461,7 +33460,7 @@
       <c r="U429" s="6"/>
       <c r="V429" s="6"/>
     </row>
-    <row r="430" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A430" s="6"/>
       <c r="B430" s="6"/>
       <c r="C430" s="6"/>
@@ -33485,7 +33484,7 @@
       <c r="U430" s="6"/>
       <c r="V430" s="6"/>
     </row>
-    <row r="431" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A431" s="6"/>
       <c r="B431" s="6"/>
       <c r="C431" s="6"/>
@@ -33509,7 +33508,7 @@
       <c r="U431" s="6"/>
       <c r="V431" s="6"/>
     </row>
-    <row r="432" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A432" s="6"/>
       <c r="B432" s="6"/>
       <c r="C432" s="6"/>
@@ -33533,7 +33532,7 @@
       <c r="U432" s="6"/>
       <c r="V432" s="6"/>
     </row>
-    <row r="433" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A433" s="6"/>
       <c r="B433" s="6"/>
       <c r="C433" s="6"/>
@@ -33557,7 +33556,7 @@
       <c r="U433" s="6"/>
       <c r="V433" s="6"/>
     </row>
-    <row r="434" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A434" s="6"/>
       <c r="B434" s="6"/>
       <c r="C434" s="6"/>
@@ -33581,7 +33580,7 @@
       <c r="U434" s="6"/>
       <c r="V434" s="6"/>
     </row>
-    <row r="435" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A435" s="6"/>
       <c r="B435" s="6"/>
       <c r="C435" s="6"/>
@@ -33605,7 +33604,7 @@
       <c r="U435" s="6"/>
       <c r="V435" s="6"/>
     </row>
-    <row r="436" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A436" s="6"/>
       <c r="B436" s="6"/>
       <c r="C436" s="6"/>
@@ -33629,7 +33628,7 @@
       <c r="U436" s="6"/>
       <c r="V436" s="6"/>
     </row>
-    <row r="437" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A437" s="6"/>
       <c r="B437" s="6"/>
       <c r="C437" s="6"/>
@@ -33653,7 +33652,7 @@
       <c r="U437" s="6"/>
       <c r="V437" s="6"/>
     </row>
-    <row r="438" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A438" s="6"/>
       <c r="B438" s="6"/>
       <c r="C438" s="6"/>
@@ -33677,7 +33676,7 @@
       <c r="U438" s="6"/>
       <c r="V438" s="6"/>
     </row>
-    <row r="439" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A439" s="6"/>
       <c r="B439" s="6"/>
       <c r="C439" s="6"/>
@@ -33701,7 +33700,7 @@
       <c r="U439" s="6"/>
       <c r="V439" s="6"/>
     </row>
-    <row r="440" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A440" s="6"/>
       <c r="B440" s="6"/>
       <c r="C440" s="6"/>
@@ -33725,7 +33724,7 @@
       <c r="U440" s="6"/>
       <c r="V440" s="6"/>
     </row>
-    <row r="441" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A441" s="6"/>
       <c r="B441" s="6"/>
       <c r="C441" s="6"/>
@@ -33749,7 +33748,7 @@
       <c r="U441" s="6"/>
       <c r="V441" s="6"/>
     </row>
-    <row r="442" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A442" s="6"/>
       <c r="B442" s="6"/>
       <c r="C442" s="6"/>
@@ -33773,7 +33772,7 @@
       <c r="U442" s="6"/>
       <c r="V442" s="6"/>
     </row>
-    <row r="443" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A443" s="6"/>
       <c r="B443" s="6"/>
       <c r="C443" s="6"/>
@@ -33797,7 +33796,7 @@
       <c r="U443" s="6"/>
       <c r="V443" s="6"/>
     </row>
-    <row r="444" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A444" s="6"/>
       <c r="B444" s="6"/>
       <c r="C444" s="6"/>
@@ -33821,7 +33820,7 @@
       <c r="U444" s="6"/>
       <c r="V444" s="6"/>
     </row>
-    <row r="445" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A445" s="6"/>
       <c r="B445" s="6"/>
       <c r="C445" s="6"/>
@@ -33845,7 +33844,7 @@
       <c r="U445" s="6"/>
       <c r="V445" s="6"/>
     </row>
-    <row r="446" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A446" s="6"/>
       <c r="B446" s="6"/>
       <c r="C446" s="6"/>
@@ -33869,7 +33868,7 @@
       <c r="U446" s="6"/>
       <c r="V446" s="6"/>
     </row>
-    <row r="447" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A447" s="6"/>
       <c r="B447" s="6"/>
       <c r="C447" s="6"/>
@@ -33893,7 +33892,7 @@
       <c r="U447" s="6"/>
       <c r="V447" s="6"/>
     </row>
-    <row r="448" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A448" s="6"/>
       <c r="B448" s="6"/>
       <c r="C448" s="6"/>
@@ -33917,7 +33916,7 @@
       <c r="U448" s="6"/>
       <c r="V448" s="6"/>
     </row>
-    <row r="449" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A449" s="6"/>
       <c r="B449" s="6"/>
       <c r="C449" s="6"/>
@@ -33941,7 +33940,7 @@
       <c r="U449" s="6"/>
       <c r="V449" s="6"/>
     </row>
-    <row r="450" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A450" s="6"/>
       <c r="B450" s="6"/>
       <c r="C450" s="6"/>
@@ -33965,7 +33964,7 @@
       <c r="U450" s="6"/>
       <c r="V450" s="6"/>
     </row>
-    <row r="451" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A451" s="6"/>
       <c r="B451" s="6"/>
       <c r="C451" s="6"/>
@@ -33989,7 +33988,7 @@
       <c r="U451" s="6"/>
       <c r="V451" s="6"/>
     </row>
-    <row r="452" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A452" s="6"/>
       <c r="B452" s="6"/>
       <c r="C452" s="6"/>
@@ -34013,7 +34012,7 @@
       <c r="U452" s="6"/>
       <c r="V452" s="6"/>
     </row>
-    <row r="453" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A453" s="6"/>
       <c r="B453" s="6"/>
       <c r="C453" s="6"/>
@@ -34037,7 +34036,7 @@
       <c r="U453" s="6"/>
       <c r="V453" s="6"/>
     </row>
-    <row r="454" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A454" s="6"/>
       <c r="B454" s="6"/>
       <c r="C454" s="6"/>
@@ -34061,7 +34060,7 @@
       <c r="U454" s="6"/>
       <c r="V454" s="6"/>
     </row>
-    <row r="455" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A455" s="6"/>
       <c r="B455" s="6"/>
       <c r="C455" s="6"/>
@@ -34085,7 +34084,7 @@
       <c r="U455" s="6"/>
       <c r="V455" s="6"/>
     </row>
-    <row r="456" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A456" s="6"/>
       <c r="B456" s="6"/>
       <c r="C456" s="6"/>
@@ -34109,7 +34108,7 @@
       <c r="U456" s="6"/>
       <c r="V456" s="6"/>
     </row>
-    <row r="457" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A457" s="6"/>
       <c r="B457" s="6"/>
       <c r="C457" s="6"/>
@@ -34133,7 +34132,7 @@
       <c r="U457" s="6"/>
       <c r="V457" s="6"/>
     </row>
-    <row r="458" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A458" s="6"/>
       <c r="B458" s="6"/>
       <c r="C458" s="6"/>
@@ -34157,7 +34156,7 @@
       <c r="U458" s="6"/>
       <c r="V458" s="6"/>
     </row>
-    <row r="459" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A459" s="6"/>
       <c r="B459" s="6"/>
       <c r="C459" s="6"/>
@@ -34181,7 +34180,7 @@
       <c r="U459" s="6"/>
       <c r="V459" s="6"/>
     </row>
-    <row r="460" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A460" s="6"/>
       <c r="B460" s="6"/>
       <c r="C460" s="6"/>
@@ -34205,7 +34204,7 @@
       <c r="U460" s="6"/>
       <c r="V460" s="6"/>
     </row>
-    <row r="461" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A461" s="6"/>
       <c r="B461" s="6"/>
       <c r="C461" s="6"/>
@@ -34229,7 +34228,7 @@
       <c r="U461" s="6"/>
       <c r="V461" s="6"/>
     </row>
-    <row r="462" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A462" s="6"/>
       <c r="B462" s="6"/>
       <c r="C462" s="6"/>
@@ -34253,7 +34252,7 @@
       <c r="U462" s="6"/>
       <c r="V462" s="6"/>
     </row>
-    <row r="463" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A463" s="6"/>
       <c r="B463" s="6"/>
       <c r="C463" s="6"/>
@@ -34277,7 +34276,7 @@
       <c r="U463" s="6"/>
       <c r="V463" s="6"/>
     </row>
-    <row r="464" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A464" s="6"/>
       <c r="B464" s="6"/>
       <c r="C464" s="6"/>
@@ -34301,7 +34300,7 @@
       <c r="U464" s="6"/>
       <c r="V464" s="6"/>
     </row>
-    <row r="465" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A465" s="6"/>
       <c r="B465" s="6"/>
       <c r="C465" s="6"/>
@@ -34325,7 +34324,7 @@
       <c r="U465" s="6"/>
       <c r="V465" s="6"/>
     </row>
-    <row r="466" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A466" s="6"/>
       <c r="B466" s="6"/>
       <c r="C466" s="6"/>
@@ -34349,7 +34348,7 @@
       <c r="U466" s="6"/>
       <c r="V466" s="6"/>
     </row>
-    <row r="467" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A467" s="6"/>
       <c r="B467" s="6"/>
       <c r="C467" s="6"/>
@@ -34373,7 +34372,7 @@
       <c r="U467" s="6"/>
       <c r="V467" s="6"/>
     </row>
-    <row r="468" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A468" s="6"/>
       <c r="B468" s="6"/>
       <c r="C468" s="6"/>
@@ -34397,7 +34396,7 @@
       <c r="U468" s="6"/>
       <c r="V468" s="6"/>
     </row>
-    <row r="469" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A469" s="6"/>
       <c r="B469" s="6"/>
       <c r="C469" s="6"/>
@@ -34421,7 +34420,7 @@
       <c r="U469" s="6"/>
       <c r="V469" s="6"/>
     </row>
-    <row r="470" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A470" s="6"/>
       <c r="B470" s="6"/>
       <c r="C470" s="6"/>
@@ -34445,7 +34444,7 @@
       <c r="U470" s="6"/>
       <c r="V470" s="6"/>
     </row>
-    <row r="471" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A471" s="6"/>
       <c r="B471" s="6"/>
       <c r="C471" s="6"/>
@@ -34469,7 +34468,7 @@
       <c r="U471" s="6"/>
       <c r="V471" s="6"/>
     </row>
-    <row r="472" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A472" s="6"/>
       <c r="B472" s="6"/>
       <c r="C472" s="6"/>
@@ -34493,7 +34492,7 @@
       <c r="U472" s="6"/>
       <c r="V472" s="6"/>
     </row>
-    <row r="473" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A473" s="6"/>
       <c r="B473" s="6"/>
       <c r="C473" s="6"/>
@@ -34517,7 +34516,7 @@
       <c r="U473" s="6"/>
       <c r="V473" s="6"/>
     </row>
-    <row r="474" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A474" s="6"/>
       <c r="B474" s="6"/>
       <c r="C474" s="6"/>
@@ -34541,7 +34540,7 @@
       <c r="U474" s="6"/>
       <c r="V474" s="6"/>
     </row>
-    <row r="475" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A475" s="6"/>
       <c r="B475" s="6"/>
       <c r="C475" s="6"/>
@@ -34565,7 +34564,7 @@
       <c r="U475" s="6"/>
       <c r="V475" s="6"/>
     </row>
-    <row r="476" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A476" s="6"/>
       <c r="B476" s="6"/>
       <c r="C476" s="6"/>
@@ -34589,7 +34588,7 @@
       <c r="U476" s="6"/>
       <c r="V476" s="6"/>
     </row>
-    <row r="477" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A477" s="6"/>
       <c r="B477" s="6"/>
       <c r="C477" s="6"/>
@@ -34613,7 +34612,7 @@
       <c r="U477" s="6"/>
       <c r="V477" s="6"/>
     </row>
-    <row r="478" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A478" s="6"/>
       <c r="B478" s="6"/>
       <c r="C478" s="6"/>
@@ -34637,7 +34636,7 @@
       <c r="U478" s="6"/>
       <c r="V478" s="6"/>
     </row>
-    <row r="479" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A479" s="6"/>
       <c r="B479" s="6"/>
       <c r="C479" s="6"/>
@@ -34661,7 +34660,7 @@
       <c r="U479" s="6"/>
       <c r="V479" s="6"/>
     </row>
-    <row r="480" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A480" s="6"/>
       <c r="B480" s="6"/>
       <c r="C480" s="6"/>
@@ -34685,7 +34684,7 @@
       <c r="U480" s="6"/>
       <c r="V480" s="6"/>
     </row>
-    <row r="481" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A481" s="6"/>
       <c r="B481" s="6"/>
       <c r="C481" s="6"/>
@@ -34709,7 +34708,7 @@
       <c r="U481" s="6"/>
       <c r="V481" s="6"/>
     </row>
-    <row r="482" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A482" s="6"/>
       <c r="B482" s="6"/>
       <c r="C482" s="6"/>
@@ -34733,7 +34732,7 @@
       <c r="U482" s="6"/>
       <c r="V482" s="6"/>
     </row>
-    <row r="483" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A483" s="6"/>
       <c r="B483" s="6"/>
       <c r="C483" s="6"/>
@@ -34771,33 +34770,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD4B3F6-F2F2-43FA-B383-9CA99EE1DED7}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X201"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -34871,7 +34870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>2024</v>
       </c>
@@ -34931,7 +34930,7 @@
       </c>
       <c r="X2" s="7"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2024</v>
       </c>
@@ -35006,7 +35005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2024</v>
       </c>
@@ -35081,7 +35080,7 @@
       </c>
       <c r="X4" s="7"/>
     </row>
-    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>2024</v>
       </c>
@@ -35156,7 +35155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2024</v>
       </c>
@@ -35231,7 +35230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>2024</v>
       </c>
@@ -35306,7 +35305,7 @@
       </c>
       <c r="X7" s="7"/>
     </row>
-    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2024</v>
       </c>
@@ -35381,7 +35380,7 @@
       </c>
       <c r="X8" s="7"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>2024</v>
       </c>
@@ -35456,7 +35455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>2024</v>
       </c>
@@ -35531,7 +35530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>2024</v>
       </c>
@@ -35606,7 +35605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>2024</v>
       </c>
@@ -35681,7 +35680,7 @@
       </c>
       <c r="X12" s="7"/>
     </row>
-    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>2024</v>
       </c>
@@ -35756,7 +35755,7 @@
       </c>
       <c r="X13" s="7"/>
     </row>
-    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2024</v>
       </c>
@@ -35831,7 +35830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>2024</v>
       </c>
@@ -35906,7 +35905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>2024</v>
       </c>
@@ -35981,7 +35980,7 @@
       </c>
       <c r="X16" s="7"/>
     </row>
-    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>2024</v>
       </c>
@@ -36056,7 +36055,7 @@
       </c>
       <c r="X17" s="7"/>
     </row>
-    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>2024</v>
       </c>
@@ -36131,7 +36130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>2024</v>
       </c>
@@ -36206,7 +36205,7 @@
       </c>
       <c r="X19" s="7"/>
     </row>
-    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>2024</v>
       </c>
@@ -36281,7 +36280,7 @@
       </c>
       <c r="X20" s="7"/>
     </row>
-    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>2024</v>
       </c>
@@ -36356,7 +36355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>2024</v>
       </c>
@@ -36431,7 +36430,7 @@
       </c>
       <c r="X22" s="7"/>
     </row>
-    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>2024</v>
       </c>
@@ -36506,7 +36505,7 @@
       </c>
       <c r="X23" s="7"/>
     </row>
-    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>2024</v>
       </c>
@@ -36581,7 +36580,7 @@
       </c>
       <c r="X24" s="7"/>
     </row>
-    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>2024</v>
       </c>
@@ -36656,7 +36655,7 @@
       </c>
       <c r="X25" s="7"/>
     </row>
-    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>2024</v>
       </c>
@@ -36731,7 +36730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>2024</v>
       </c>
@@ -36806,7 +36805,7 @@
       </c>
       <c r="X27" s="7"/>
     </row>
-    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>2024</v>
       </c>
@@ -36881,7 +36880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>2024</v>
       </c>
@@ -36956,7 +36955,7 @@
       </c>
       <c r="X29" s="7"/>
     </row>
-    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>2024</v>
       </c>
@@ -37031,7 +37030,7 @@
       </c>
       <c r="X30" s="7"/>
     </row>
-    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>2024</v>
       </c>
@@ -37106,7 +37105,7 @@
       </c>
       <c r="X31" s="7"/>
     </row>
-    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>2024</v>
       </c>
@@ -37181,7 +37180,7 @@
       </c>
       <c r="X32" s="7"/>
     </row>
-    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>2024</v>
       </c>
@@ -37256,7 +37255,7 @@
       </c>
       <c r="X33" s="7"/>
     </row>
-    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>2024</v>
       </c>
@@ -37331,7 +37330,7 @@
       </c>
       <c r="X34" s="7"/>
     </row>
-    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>2024</v>
       </c>
@@ -37406,7 +37405,7 @@
       </c>
       <c r="X35" s="7"/>
     </row>
-    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>2024</v>
       </c>
@@ -37481,7 +37480,7 @@
       </c>
       <c r="X36" s="7"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>2024</v>
       </c>
@@ -37556,7 +37555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>2024</v>
       </c>
@@ -37631,7 +37630,7 @@
       </c>
       <c r="X38" s="7"/>
     </row>
-    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>2024</v>
       </c>
@@ -37706,7 +37705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>2024</v>
       </c>
@@ -37781,7 +37780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>2024</v>
       </c>
@@ -37856,7 +37855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>2024</v>
       </c>
@@ -37931,7 +37930,7 @@
       </c>
       <c r="X42" s="7"/>
     </row>
-    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>2024</v>
       </c>
@@ -38006,7 +38005,7 @@
       </c>
       <c r="X43" s="7"/>
     </row>
-    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>2024</v>
       </c>
@@ -38081,7 +38080,7 @@
       </c>
       <c r="X44" s="7"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>2024</v>
       </c>
@@ -38156,7 +38155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>2024</v>
       </c>
@@ -38231,7 +38230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>2024</v>
       </c>
@@ -38306,7 +38305,7 @@
       </c>
       <c r="X47" s="7"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>2024</v>
       </c>
@@ -38381,7 +38380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>2024</v>
       </c>
@@ -38456,7 +38455,7 @@
       </c>
       <c r="X49" s="7"/>
     </row>
-    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>2024</v>
       </c>
@@ -38531,7 +38530,7 @@
       </c>
       <c r="X50" s="7"/>
     </row>
-    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>2024</v>
       </c>
@@ -38606,7 +38605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>2024</v>
       </c>
@@ -38681,7 +38680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>2024</v>
       </c>
@@ -38756,7 +38755,7 @@
       </c>
       <c r="X53" s="7"/>
     </row>
-    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>2024</v>
       </c>
@@ -38831,7 +38830,7 @@
       </c>
       <c r="X54" s="7"/>
     </row>
-    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>2024</v>
       </c>
@@ -38906,7 +38905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>2024</v>
       </c>
@@ -38981,7 +38980,7 @@
       </c>
       <c r="X56" s="7"/>
     </row>
-    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>2024</v>
       </c>
@@ -39056,7 +39055,7 @@
       </c>
       <c r="X57" s="7"/>
     </row>
-    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>2024</v>
       </c>
@@ -39131,7 +39130,7 @@
       </c>
       <c r="X58" s="7"/>
     </row>
-    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>2024</v>
       </c>
@@ -39206,7 +39205,7 @@
       </c>
       <c r="X59" s="7"/>
     </row>
-    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>2024</v>
       </c>
@@ -39281,7 +39280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>2024</v>
       </c>
@@ -39356,7 +39355,7 @@
       </c>
       <c r="X61" s="7"/>
     </row>
-    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>2024</v>
       </c>
@@ -39431,7 +39430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>2024</v>
       </c>
@@ -39506,7 +39505,7 @@
       </c>
       <c r="X63" s="7"/>
     </row>
-    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>2024</v>
       </c>
@@ -39581,7 +39580,7 @@
       </c>
       <c r="X64" s="7"/>
     </row>
-    <row r="65" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>2024</v>
       </c>
@@ -39656,7 +39655,7 @@
       </c>
       <c r="X65" s="7"/>
     </row>
-    <row r="66" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>2024</v>
       </c>
@@ -39731,7 +39730,7 @@
       </c>
       <c r="X66" s="7"/>
     </row>
-    <row r="67" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>2024</v>
       </c>
@@ -39806,7 +39805,7 @@
       </c>
       <c r="X67" s="7"/>
     </row>
-    <row r="68" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>2024</v>
       </c>
@@ -39881,7 +39880,7 @@
       </c>
       <c r="X68" s="7"/>
     </row>
-    <row r="69" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>2024</v>
       </c>
@@ -39956,7 +39955,7 @@
       </c>
       <c r="X69" s="7"/>
     </row>
-    <row r="70" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>2024</v>
       </c>
@@ -40031,7 +40030,7 @@
       </c>
       <c r="X70" s="7"/>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>2024</v>
       </c>
@@ -40106,7 +40105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>2024</v>
       </c>
@@ -40181,7 +40180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>2024</v>
       </c>
@@ -40256,7 +40255,7 @@
       </c>
       <c r="X73" s="7"/>
     </row>
-    <row r="74" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>2024</v>
       </c>
@@ -40331,7 +40330,7 @@
       </c>
       <c r="X74" s="7"/>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>2024</v>
       </c>
@@ -40406,7 +40405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>2024</v>
       </c>
@@ -40481,7 +40480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>2024</v>
       </c>
@@ -40556,7 +40555,7 @@
       </c>
       <c r="X77" s="7"/>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>2024</v>
       </c>
@@ -40631,7 +40630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>2024</v>
       </c>
@@ -40706,7 +40705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>2024</v>
       </c>
@@ -40778,7 +40777,7 @@
       </c>
       <c r="X80" s="7"/>
     </row>
-    <row r="81" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>2024</v>
       </c>
@@ -40853,7 +40852,7 @@
       </c>
       <c r="X81" s="7"/>
     </row>
-    <row r="82" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7">
         <v>2024</v>
       </c>
@@ -40928,7 +40927,7 @@
       </c>
       <c r="X82" s="7"/>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>2024</v>
       </c>
@@ -41003,7 +41002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
         <v>2024</v>
       </c>
@@ -41078,7 +41077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>2024</v>
       </c>
@@ -41153,7 +41152,7 @@
       </c>
       <c r="X85" s="7"/>
     </row>
-    <row r="86" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
         <v>2024</v>
       </c>
@@ -41228,7 +41227,7 @@
       </c>
       <c r="X86" s="7"/>
     </row>
-    <row r="87" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>2024</v>
       </c>
@@ -41303,7 +41302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
         <v>2024</v>
       </c>
@@ -41378,7 +41377,7 @@
       </c>
       <c r="X88" s="7"/>
     </row>
-    <row r="89" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
         <v>2024</v>
       </c>
@@ -41453,7 +41452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
         <v>2024</v>
       </c>
@@ -41528,7 +41527,7 @@
       </c>
       <c r="X90" s="7"/>
     </row>
-    <row r="91" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
         <v>2024</v>
       </c>
@@ -41603,7 +41602,7 @@
       </c>
       <c r="X91" s="7"/>
     </row>
-    <row r="92" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>2024</v>
       </c>
@@ -41678,7 +41677,7 @@
       </c>
       <c r="X92" s="7"/>
     </row>
-    <row r="93" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
         <v>2024</v>
       </c>
@@ -41753,7 +41752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
         <v>2024</v>
       </c>
@@ -41828,7 +41827,7 @@
       </c>
       <c r="X94" s="7"/>
     </row>
-    <row r="95" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
         <v>2024</v>
       </c>
@@ -41903,7 +41902,7 @@
       </c>
       <c r="X95" s="7"/>
     </row>
-    <row r="96" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
         <v>2024</v>
       </c>
@@ -41978,7 +41977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
         <v>2024</v>
       </c>
@@ -42053,7 +42052,7 @@
       </c>
       <c r="X97" s="7"/>
     </row>
-    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
         <v>2024</v>
       </c>
@@ -42128,7 +42127,7 @@
       </c>
       <c r="X98" s="7"/>
     </row>
-    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
         <v>2024</v>
       </c>
@@ -42203,7 +42202,7 @@
       </c>
       <c r="X99" s="7"/>
     </row>
-    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
         <v>2024</v>
       </c>
@@ -42278,7 +42277,7 @@
       </c>
       <c r="X100" s="7"/>
     </row>
-    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="7">
         <v>2024</v>
       </c>
@@ -42353,7 +42352,7 @@
       </c>
       <c r="X101" s="7"/>
     </row>
-    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
         <v>2024</v>
       </c>
@@ -42428,7 +42427,7 @@
       </c>
       <c r="X102" s="7"/>
     </row>
-    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
         <v>2024</v>
       </c>
@@ -42503,7 +42502,7 @@
       </c>
       <c r="X103" s="7"/>
     </row>
-    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
         <v>2024</v>
       </c>
@@ -42578,7 +42577,7 @@
       </c>
       <c r="X104" s="7"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
         <v>2024</v>
       </c>
@@ -42653,7 +42652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
         <v>2024</v>
       </c>
@@ -42728,7 +42727,7 @@
       </c>
       <c r="X106" s="7"/>
     </row>
-    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
         <v>2024</v>
       </c>
@@ -42803,7 +42802,7 @@
       </c>
       <c r="X107" s="7"/>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
         <v>2024</v>
       </c>
@@ -42878,7 +42877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
         <v>2024</v>
       </c>
@@ -42953,7 +42952,7 @@
       </c>
       <c r="X109" s="7"/>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
         <v>2024</v>
       </c>
@@ -43028,7 +43027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
         <v>2024</v>
       </c>
@@ -43103,7 +43102,7 @@
       </c>
       <c r="X111" s="7"/>
     </row>
-    <row r="112" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
         <v>2024</v>
       </c>
@@ -43178,7 +43177,7 @@
       </c>
       <c r="X112" s="7"/>
     </row>
-    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
         <v>2024</v>
       </c>
@@ -43253,7 +43252,7 @@
       </c>
       <c r="X113" s="7"/>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" s="7">
         <v>2024</v>
       </c>
@@ -43328,7 +43327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="7">
         <v>2024</v>
       </c>
@@ -43403,7 +43402,7 @@
       </c>
       <c r="X115" s="7"/>
     </row>
-    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="7">
         <v>2024</v>
       </c>
@@ -43478,7 +43477,7 @@
       </c>
       <c r="X116" s="7"/>
     </row>
-    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="7">
         <v>2024</v>
       </c>
@@ -43553,7 +43552,7 @@
       </c>
       <c r="X117" s="7"/>
     </row>
-    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="7">
         <v>2024</v>
       </c>
@@ -43628,7 +43627,7 @@
       </c>
       <c r="X118" s="7"/>
     </row>
-    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="7">
         <v>2024</v>
       </c>
@@ -43703,7 +43702,7 @@
       </c>
       <c r="X119" s="7"/>
     </row>
-    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="7">
         <v>2024</v>
       </c>
@@ -43778,7 +43777,7 @@
       </c>
       <c r="X120" s="7"/>
     </row>
-    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="7">
         <v>2024</v>
       </c>
@@ -43853,7 +43852,7 @@
       </c>
       <c r="X121" s="7"/>
     </row>
-    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="7">
         <v>2024</v>
       </c>
@@ -43928,7 +43927,7 @@
       </c>
       <c r="X122" s="7"/>
     </row>
-    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="7">
         <v>2024</v>
       </c>
@@ -43999,7 +43998,7 @@
       <c r="W123" s="10"/>
       <c r="X123" s="7"/>
     </row>
-    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="7">
         <v>2024</v>
       </c>
@@ -44074,7 +44073,7 @@
       </c>
       <c r="X124" s="7"/>
     </row>
-    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="7">
         <v>2024</v>
       </c>
@@ -44149,7 +44148,7 @@
       </c>
       <c r="X125" s="7"/>
     </row>
-    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="7">
         <v>2024</v>
       </c>
@@ -44224,7 +44223,7 @@
       </c>
       <c r="X126" s="7"/>
     </row>
-    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="7">
         <v>2024</v>
       </c>
@@ -44299,7 +44298,7 @@
       </c>
       <c r="X127" s="7"/>
     </row>
-    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="7">
         <v>2024</v>
       </c>
@@ -44374,7 +44373,7 @@
       </c>
       <c r="X128" s="7"/>
     </row>
-    <row r="129" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="7">
         <v>2024</v>
       </c>
@@ -44449,7 +44448,7 @@
       </c>
       <c r="X129" s="7"/>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" s="7">
         <v>2024</v>
       </c>
@@ -44524,7 +44523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" s="7">
         <v>2024</v>
       </c>
@@ -44599,7 +44598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" s="7">
         <v>2024</v>
       </c>
@@ -44674,7 +44673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" s="7">
         <v>2024</v>
       </c>
@@ -44749,7 +44748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" s="7">
         <v>2024</v>
       </c>
@@ -44824,7 +44823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" s="7">
         <v>2024</v>
       </c>
@@ -44899,7 +44898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <v>2024</v>
       </c>
@@ -44974,7 +44973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" s="7">
         <v>2024</v>
       </c>
@@ -45049,7 +45048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -45073,7 +45072,7 @@
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
     </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -45097,7 +45096,7 @@
       <c r="U139" s="4"/>
       <c r="V139" s="4"/>
     </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -45121,7 +45120,7 @@
       <c r="U140" s="4"/>
       <c r="V140" s="4"/>
     </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -45145,7 +45144,7 @@
       <c r="U141" s="4"/>
       <c r="V141" s="4"/>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -45169,7 +45168,7 @@
       <c r="U142" s="4"/>
       <c r="V142" s="4"/>
     </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -45193,7 +45192,7 @@
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
     </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -45217,7 +45216,7 @@
       <c r="U144" s="4"/>
       <c r="V144" s="4"/>
     </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -45241,7 +45240,7 @@
       <c r="U145" s="4"/>
       <c r="V145" s="4"/>
     </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -45265,7 +45264,7 @@
       <c r="U146" s="4"/>
       <c r="V146" s="4"/>
     </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -45289,7 +45288,7 @@
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
     </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -45313,7 +45312,7 @@
       <c r="U148" s="4"/>
       <c r="V148" s="4"/>
     </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -45337,7 +45336,7 @@
       <c r="U149" s="4"/>
       <c r="V149" s="4"/>
     </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -45361,7 +45360,7 @@
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
     </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -45385,7 +45384,7 @@
       <c r="U151" s="4"/>
       <c r="V151" s="4"/>
     </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -45409,7 +45408,7 @@
       <c r="U152" s="4"/>
       <c r="V152" s="4"/>
     </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -45433,7 +45432,7 @@
       <c r="U153" s="4"/>
       <c r="V153" s="4"/>
     </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -45457,7 +45456,7 @@
       <c r="U154" s="4"/>
       <c r="V154" s="4"/>
     </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -45481,7 +45480,7 @@
       <c r="U155" s="4"/>
       <c r="V155" s="4"/>
     </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -45505,7 +45504,7 @@
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
     </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -45529,7 +45528,7 @@
       <c r="U157" s="4"/>
       <c r="V157" s="4"/>
     </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -45553,7 +45552,7 @@
       <c r="U158" s="4"/>
       <c r="V158" s="4"/>
     </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -45577,7 +45576,7 @@
       <c r="U159" s="4"/>
       <c r="V159" s="4"/>
     </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -45601,7 +45600,7 @@
       <c r="U160" s="4"/>
       <c r="V160" s="4"/>
     </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -45625,7 +45624,7 @@
       <c r="U161" s="4"/>
       <c r="V161" s="4"/>
     </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -45649,7 +45648,7 @@
       <c r="U162" s="4"/>
       <c r="V162" s="4"/>
     </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -45673,7 +45672,7 @@
       <c r="U163" s="4"/>
       <c r="V163" s="4"/>
     </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -45697,7 +45696,7 @@
       <c r="U164" s="4"/>
       <c r="V164" s="4"/>
     </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -45721,7 +45720,7 @@
       <c r="U165" s="4"/>
       <c r="V165" s="4"/>
     </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -45745,7 +45744,7 @@
       <c r="U166" s="4"/>
       <c r="V166" s="4"/>
     </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -45769,7 +45768,7 @@
       <c r="U167" s="4"/>
       <c r="V167" s="4"/>
     </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -45793,7 +45792,7 @@
       <c r="U168" s="4"/>
       <c r="V168" s="4"/>
     </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -45817,7 +45816,7 @@
       <c r="U169" s="4"/>
       <c r="V169" s="4"/>
     </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -45841,7 +45840,7 @@
       <c r="U170" s="4"/>
       <c r="V170" s="4"/>
     </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -45865,7 +45864,7 @@
       <c r="U171" s="4"/>
       <c r="V171" s="4"/>
     </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -45889,7 +45888,7 @@
       <c r="U172" s="4"/>
       <c r="V172" s="4"/>
     </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -45913,7 +45912,7 @@
       <c r="U173" s="4"/>
       <c r="V173" s="4"/>
     </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -45937,7 +45936,7 @@
       <c r="U174" s="4"/>
       <c r="V174" s="4"/>
     </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -45961,7 +45960,7 @@
       <c r="U175" s="4"/>
       <c r="V175" s="4"/>
     </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -45985,7 +45984,7 @@
       <c r="U176" s="4"/>
       <c r="V176" s="4"/>
     </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -46009,7 +46008,7 @@
       <c r="U177" s="4"/>
       <c r="V177" s="4"/>
     </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -46033,7 +46032,7 @@
       <c r="U178" s="4"/>
       <c r="V178" s="4"/>
     </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -46057,7 +46056,7 @@
       <c r="U179" s="4"/>
       <c r="V179" s="4"/>
     </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -46081,7 +46080,7 @@
       <c r="U180" s="4"/>
       <c r="V180" s="4"/>
     </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -46105,7 +46104,7 @@
       <c r="U181" s="4"/>
       <c r="V181" s="4"/>
     </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -46129,7 +46128,7 @@
       <c r="U182" s="4"/>
       <c r="V182" s="4"/>
     </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -46153,7 +46152,7 @@
       <c r="U183" s="4"/>
       <c r="V183" s="4"/>
     </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -46177,7 +46176,7 @@
       <c r="U184" s="4"/>
       <c r="V184" s="4"/>
     </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -46201,7 +46200,7 @@
       <c r="U185" s="4"/>
       <c r="V185" s="4"/>
     </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -46225,7 +46224,7 @@
       <c r="U186" s="4"/>
       <c r="V186" s="4"/>
     </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -46249,7 +46248,7 @@
       <c r="U187" s="4"/>
       <c r="V187" s="4"/>
     </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -46273,7 +46272,7 @@
       <c r="U188" s="4"/>
       <c r="V188" s="4"/>
     </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -46297,7 +46296,7 @@
       <c r="U189" s="4"/>
       <c r="V189" s="4"/>
     </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -46321,7 +46320,7 @@
       <c r="U190" s="4"/>
       <c r="V190" s="4"/>
     </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -46345,7 +46344,7 @@
       <c r="U191" s="4"/>
       <c r="V191" s="4"/>
     </row>
-    <row r="192" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -46369,7 +46368,7 @@
       <c r="U192" s="4"/>
       <c r="V192" s="4"/>
     </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -46393,7 +46392,7 @@
       <c r="U193" s="4"/>
       <c r="V193" s="4"/>
     </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -46417,7 +46416,7 @@
       <c r="U194" s="4"/>
       <c r="V194" s="4"/>
     </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -46441,7 +46440,7 @@
       <c r="U195" s="4"/>
       <c r="V195" s="4"/>
     </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -46465,7 +46464,7 @@
       <c r="U196" s="4"/>
       <c r="V196" s="4"/>
     </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -46489,7 +46488,7 @@
       <c r="U197" s="4"/>
       <c r="V197" s="4"/>
     </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -46513,7 +46512,7 @@
       <c r="U198" s="4"/>
       <c r="V198" s="4"/>
     </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -46537,7 +46536,7 @@
       <c r="U199" s="4"/>
       <c r="V199" s="4"/>
     </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -46561,7 +46560,7 @@
       <c r="U200" s="4"/>
       <c r="V200" s="4"/>
     </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -46602,32 +46601,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F7ED7A-89EF-4D25-B9EF-C92C4F4899FE}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X268"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="5.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -46701,7 +46700,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2025</v>
       </c>
@@ -46776,7 +46775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -46851,7 +46850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2025</v>
       </c>
@@ -46926,7 +46925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2025</v>
       </c>
@@ -47001,7 +47000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2025</v>
       </c>
@@ -47076,7 +47075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2025</v>
       </c>
@@ -47151,7 +47150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2025</v>
       </c>
@@ -47226,7 +47225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2025</v>
       </c>
@@ -47301,7 +47300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>2025</v>
       </c>
@@ -47376,7 +47375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -47451,7 +47450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2025</v>
       </c>
@@ -47526,7 +47525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2025</v>
       </c>
@@ -47601,7 +47600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>2025</v>
       </c>
@@ -47676,7 +47675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2025</v>
       </c>
@@ -47751,7 +47750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>2025</v>
       </c>
@@ -47826,7 +47825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -47901,7 +47900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>2025</v>
       </c>
@@ -47976,7 +47975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2025</v>
       </c>
@@ -48051,7 +48050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>2025</v>
       </c>
@@ -48126,7 +48125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2025</v>
       </c>
@@ -48201,7 +48200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>2025</v>
       </c>
@@ -48276,7 +48275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2025</v>
       </c>
@@ -48351,7 +48350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>2025</v>
       </c>
@@ -48426,7 +48425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2025</v>
       </c>
@@ -48501,7 +48500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>2025</v>
       </c>
@@ -48576,7 +48575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2025</v>
       </c>
@@ -48651,7 +48650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>2025</v>
       </c>
@@ -48726,7 +48725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2025</v>
       </c>
@@ -48801,7 +48800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2025</v>
       </c>
@@ -48876,7 +48875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2025</v>
       </c>
@@ -48951,7 +48950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2025</v>
       </c>
@@ -49026,7 +49025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2025</v>
       </c>
@@ -49101,7 +49100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2025</v>
       </c>
@@ -49176,7 +49175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2025</v>
       </c>
@@ -49251,7 +49250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2025</v>
       </c>
@@ -49326,7 +49325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2025</v>
       </c>
@@ -49401,7 +49400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2025</v>
       </c>
@@ -49476,7 +49475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2025</v>
       </c>
@@ -49551,7 +49550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2025</v>
       </c>
@@ -49626,7 +49625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2025</v>
       </c>
@@ -49701,7 +49700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2025</v>
       </c>
@@ -49776,7 +49775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2025</v>
       </c>
@@ -49851,7 +49850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2025</v>
       </c>
@@ -49926,7 +49925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2025</v>
       </c>
@@ -50001,7 +50000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2025</v>
       </c>
@@ -50076,7 +50075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2025</v>
       </c>
@@ -50151,7 +50150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2025</v>
       </c>
@@ -50226,7 +50225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2025</v>
       </c>
@@ -50301,7 +50300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2025</v>
       </c>
@@ -50376,7 +50375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2025</v>
       </c>
@@ -50451,7 +50450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2025</v>
       </c>
@@ -50526,7 +50525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2025</v>
       </c>
@@ -50601,7 +50600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>2025</v>
       </c>
@@ -50676,7 +50675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2025</v>
       </c>
@@ -50751,7 +50750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>2025</v>
       </c>
@@ -50826,7 +50825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2025</v>
       </c>
@@ -50901,7 +50900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>2025</v>
       </c>
@@ -50976,7 +50975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2025</v>
       </c>
@@ -51051,7 +51050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>2025</v>
       </c>
@@ -51126,7 +51125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2025</v>
       </c>
@@ -51201,7 +51200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>2025</v>
       </c>
@@ -51276,7 +51275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2025</v>
       </c>
@@ -51351,7 +51350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>2025</v>
       </c>
@@ -51426,7 +51425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>2025</v>
       </c>
@@ -51501,7 +51500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>2025</v>
       </c>
@@ -51576,7 +51575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>2025</v>
       </c>
@@ -51651,7 +51650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>2025</v>
       </c>
@@ -51726,7 +51725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>2025</v>
       </c>
@@ -51801,7 +51800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>2025</v>
       </c>
@@ -51876,7 +51875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>2025</v>
       </c>
@@ -51951,7 +51950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>2025</v>
       </c>
@@ -52026,7 +52025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>2025</v>
       </c>
@@ -52101,7 +52100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>2025</v>
       </c>
@@ -52176,7 +52175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>2025</v>
       </c>
@@ -52251,7 +52250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>2025</v>
       </c>
@@ -52326,7 +52325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>2025</v>
       </c>
@@ -52401,7 +52400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>2025</v>
       </c>
@@ -52476,7 +52475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>2025</v>
       </c>
@@ -52551,7 +52550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>2025</v>
       </c>
@@ -52626,7 +52625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>2025</v>
       </c>
@@ -52701,7 +52700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>2025</v>
       </c>
@@ -52776,7 +52775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>2025</v>
       </c>
@@ -52851,7 +52850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>2025</v>
       </c>
@@ -52926,7 +52925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>2025</v>
       </c>
@@ -53001,7 +53000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>2025</v>
       </c>
@@ -53076,7 +53075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>2025</v>
       </c>
@@ -53151,7 +53150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>2025</v>
       </c>
@@ -53226,7 +53225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>2025</v>
       </c>
@@ -53301,7 +53300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>2025</v>
       </c>
@@ -53376,7 +53375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>2025</v>
       </c>
@@ -53451,7 +53450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>2025</v>
       </c>
@@ -53526,7 +53525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>2025</v>
       </c>
@@ -53601,7 +53600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>2025</v>
       </c>
@@ -53676,7 +53675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>2025</v>
       </c>
@@ -53751,7 +53750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>2025</v>
       </c>
@@ -53826,7 +53825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>2025</v>
       </c>
@@ -53901,7 +53900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>2025</v>
       </c>
@@ -53976,7 +53975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>2025</v>
       </c>
@@ -54051,7 +54050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>2025</v>
       </c>
@@ -54126,7 +54125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>2025</v>
       </c>
@@ -54201,7 +54200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>2025</v>
       </c>
@@ -54276,7 +54275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>2025</v>
       </c>
@@ -54351,7 +54350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>2025</v>
       </c>
@@ -54426,7 +54425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>2025</v>
       </c>
@@ -54501,7 +54500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>2025</v>
       </c>
@@ -54576,7 +54575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>2025</v>
       </c>
@@ -54651,7 +54650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>2025</v>
       </c>
@@ -54726,7 +54725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>2025</v>
       </c>
@@ -54801,7 +54800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>2025</v>
       </c>
@@ -54876,7 +54875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>2025</v>
       </c>
@@ -54951,7 +54950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>2025</v>
       </c>
@@ -55026,7 +55025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>2025</v>
       </c>
@@ -55101,7 +55100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>2025</v>
       </c>
@@ -55176,7 +55175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>2025</v>
       </c>
@@ -55251,7 +55250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>2025</v>
       </c>
@@ -55326,7 +55325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>2025</v>
       </c>
@@ -55401,7 +55400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>2025</v>
       </c>
@@ -55476,7 +55475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>2025</v>
       </c>
@@ -55551,7 +55550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>2025</v>
       </c>
@@ -55626,7 +55625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>2025</v>
       </c>
@@ -55701,7 +55700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>2025</v>
       </c>
@@ -55776,7 +55775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>2025</v>
       </c>
@@ -55851,7 +55850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>2025</v>
       </c>
@@ -55926,7 +55925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>2025</v>
       </c>
@@ -56001,7 +56000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>2025</v>
       </c>
@@ -56076,7 +56075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>2025</v>
       </c>
@@ -56151,7 +56150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>2025</v>
       </c>
@@ -56226,7 +56225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>2025</v>
       </c>
@@ -56301,7 +56300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>2025</v>
       </c>
@@ -56376,7 +56375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>2025</v>
       </c>
@@ -56451,7 +56450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>2025</v>
       </c>
@@ -56526,7 +56525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>2025</v>
       </c>
@@ -56601,7 +56600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>2025</v>
       </c>
@@ -56676,7 +56675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>2025</v>
       </c>
@@ -56751,7 +56750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>2025</v>
       </c>
@@ -56826,7 +56825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>2025</v>
       </c>
@@ -56901,7 +56900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>2025</v>
       </c>
@@ -56976,7 +56975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>2025</v>
       </c>
@@ -57051,7 +57050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>2025</v>
       </c>
@@ -57126,7 +57125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>2025</v>
       </c>
@@ -57201,7 +57200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>2025</v>
       </c>
@@ -57276,7 +57275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>2025</v>
       </c>
@@ -57351,7 +57350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>2025</v>
       </c>
@@ -57426,7 +57425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>2025</v>
       </c>
@@ -57501,7 +57500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>2025</v>
       </c>
@@ -57576,7 +57575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>2025</v>
       </c>
@@ -57651,7 +57650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>2025</v>
       </c>
@@ -57726,7 +57725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>2025</v>
       </c>
@@ -57801,7 +57800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>2025</v>
       </c>
@@ -57876,7 +57875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>2025</v>
       </c>
@@ -57951,7 +57950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>2025</v>
       </c>
@@ -58026,7 +58025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>2025</v>
       </c>
@@ -58101,7 +58100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>2025</v>
       </c>
@@ -58176,7 +58175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>2025</v>
       </c>
@@ -58251,7 +58250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>2025</v>
       </c>
@@ -58326,7 +58325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
         <v>2025</v>
       </c>
@@ -58401,7 +58400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>2025</v>
       </c>
@@ -58476,7 +58475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>2025</v>
       </c>
@@ -58551,7 +58550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>2025</v>
       </c>
@@ -58626,7 +58625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>2025</v>
       </c>
@@ -58701,7 +58700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>2025</v>
       </c>
@@ -58776,7 +58775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
         <v>2025</v>
       </c>
@@ -58851,7 +58850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>2025</v>
       </c>
@@ -58926,7 +58925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
         <v>2025</v>
       </c>
@@ -59001,7 +59000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>2025</v>
       </c>
@@ -59076,7 +59075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
         <v>2025</v>
       </c>
@@ -59151,7 +59150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>2025</v>
       </c>
@@ -59226,7 +59225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
         <v>2025</v>
       </c>
@@ -59301,7 +59300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>2025</v>
       </c>
@@ -59376,7 +59375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
         <v>2025</v>
       </c>
@@ -59451,7 +59450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>2025</v>
       </c>
@@ -59526,7 +59525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
         <v>2025</v>
       </c>
@@ -59601,7 +59600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>2025</v>
       </c>
@@ -59676,7 +59675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>2025</v>
       </c>
@@ -59751,7 +59750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>2025</v>
       </c>
@@ -59826,7 +59825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>2025</v>
       </c>
@@ -59901,7 +59900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>2025</v>
       </c>
@@ -59976,7 +59975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>2025</v>
       </c>
@@ -60051,7 +60050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>2025</v>
       </c>
@@ -60126,7 +60125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
         <v>2025</v>
       </c>
@@ -60201,7 +60200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>2025</v>
       </c>
@@ -60276,7 +60275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
         <v>2025</v>
       </c>
@@ -60351,7 +60350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>2025</v>
       </c>
@@ -60426,7 +60425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
         <v>2025</v>
       </c>
@@ -60501,7 +60500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>2025</v>
       </c>
@@ -60576,7 +60575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
         <v>2025</v>
       </c>
@@ -60651,7 +60650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>2025</v>
       </c>
@@ -60726,7 +60725,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
         <v>2025</v>
       </c>
@@ -60801,7 +60800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>2025</v>
       </c>
@@ -60876,7 +60875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
         <v>2025</v>
       </c>
@@ -60951,7 +60950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>2025</v>
       </c>
@@ -61026,7 +61025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
         <v>2025</v>
       </c>
@@ -61101,7 +61100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>2025</v>
       </c>
@@ -61176,7 +61175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
         <v>2025</v>
       </c>
@@ -61251,7 +61250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>2025</v>
       </c>
@@ -61326,7 +61325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
         <v>2025</v>
       </c>
@@ -61401,7 +61400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>2025</v>
       </c>
@@ -61476,7 +61475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
         <v>2025</v>
       </c>
@@ -61551,7 +61550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>2025</v>
       </c>
@@ -61626,7 +61625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
         <v>2025</v>
       </c>
@@ -61701,7 +61700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
         <v>2025</v>
       </c>
@@ -61776,7 +61775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
         <v>2025</v>
       </c>
@@ -61851,7 +61850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
         <v>2025</v>
       </c>
@@ -61926,7 +61925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
         <v>2025</v>
       </c>
@@ -62001,7 +62000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>2025</v>
       </c>
@@ -62076,7 +62075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
         <v>2025</v>
       </c>
@@ -62151,7 +62150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
         <v>2025</v>
       </c>
@@ -62226,7 +62225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
         <v>2025</v>
       </c>
@@ -62301,7 +62300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>2025</v>
       </c>
@@ -62376,7 +62375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
         <v>2025</v>
       </c>
@@ -62451,7 +62450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
         <v>2025</v>
       </c>
@@ -62526,7 +62525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
         <v>2025</v>
       </c>
@@ -62601,7 +62600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>2025</v>
       </c>
@@ -62676,7 +62675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
         <v>2025</v>
       </c>
@@ -62751,7 +62750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>2025</v>
       </c>
@@ -62826,7 +62825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
         <v>2025</v>
       </c>
@@ -62901,7 +62900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>2025</v>
       </c>
@@ -62976,7 +62975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
         <v>2025</v>
       </c>
@@ -63051,7 +63050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
         <v>2025</v>
       </c>
@@ -63126,7 +63125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
         <v>2025</v>
       </c>
@@ -63201,7 +63200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>2025</v>
       </c>
@@ -63276,7 +63275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
         <v>2025</v>
       </c>
@@ -63351,7 +63350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>2025</v>
       </c>
@@ -63426,7 +63425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
         <v>2025</v>
       </c>
@@ -63501,7 +63500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>2025</v>
       </c>
@@ -63576,7 +63575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>2025</v>
       </c>
@@ -63651,7 +63650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>2025</v>
       </c>
@@ -63726,7 +63725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
         <v>2025</v>
       </c>
@@ -63801,7 +63800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
         <v>2025</v>
       </c>
@@ -63876,7 +63875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
         <v>2025</v>
       </c>
@@ -63951,7 +63950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>2025</v>
       </c>
@@ -64026,7 +64025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
         <v>2025</v>
       </c>
@@ -64101,7 +64100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>2025</v>
       </c>
@@ -64176,7 +64175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
         <v>2025</v>
       </c>
@@ -64251,7 +64250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>2025</v>
       </c>
@@ -64326,7 +64325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
         <v>2025</v>
       </c>
@@ -64401,7 +64400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>2025</v>
       </c>
@@ -64476,7 +64475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <v>2025</v>
       </c>
@@ -64551,7 +64550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
         <v>2025</v>
       </c>
@@ -64626,7 +64625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
         <v>2025</v>
       </c>
@@ -64701,7 +64700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>2025</v>
       </c>
@@ -64776,7 +64775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="3">
         <v>2025</v>
       </c>
@@ -64851,7 +64850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>2025</v>
       </c>
@@ -64926,7 +64925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
         <v>2025</v>
       </c>
@@ -65001,7 +65000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>2025</v>
       </c>
@@ -65076,7 +65075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
         <v>2025</v>
       </c>
@@ -65151,7 +65150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
         <v>2025</v>
       </c>
@@ -65226,7 +65225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="3">
         <v>2025</v>
       </c>
@@ -65301,7 +65300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>2025</v>
       </c>
@@ -65376,7 +65375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
         <v>2025</v>
       </c>
@@ -65451,7 +65450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
         <v>2025</v>
       </c>
@@ -65526,7 +65525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="3">
         <v>2025</v>
       </c>
@@ -65601,7 +65600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="3">
         <v>2025</v>
       </c>
@@ -65676,7 +65675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="3">
         <v>2025</v>
       </c>
@@ -65751,7 +65750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="3">
         <v>2025</v>
       </c>
@@ -65826,7 +65825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="3">
         <v>2025</v>
       </c>
@@ -65901,7 +65900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
         <v>2025</v>
       </c>
@@ -65976,7 +65975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="3">
         <v>2025</v>
       </c>
@@ -66051,7 +66050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
         <v>2025</v>
       </c>
@@ -66126,7 +66125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="3">
         <v>2025</v>
       </c>
@@ -66201,7 +66200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>2025</v>
       </c>
@@ -66276,7 +66275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="3">
         <v>2025</v>
       </c>
@@ -66351,7 +66350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
         <v>2025</v>
       </c>
@@ -66426,7 +66425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="3">
         <v>2025</v>
       </c>
@@ -66501,7 +66500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="3">
         <v>2025</v>
       </c>
@@ -66576,7 +66575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="3">
         <v>2025</v>
       </c>
@@ -66651,7 +66650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="3">
         <v>2025</v>
       </c>
@@ -66731,12 +66730,6 @@
     <filterColumn colId="11">
       <filters>
         <filter val="PVL03"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="12">
-      <filters>
-        <filter val="Check"/>
-        <filter val="UTC"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -66746,25 +66739,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b2843789-6ce0-4c67-8bf3-b5ed13cce4b2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100928B16406DF24E43A98D222CE34F1EF2" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c096b0cb6809c35262818d47acb86f92">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b2843789-6ce0-4c67-8bf3-b5ed13cce4b2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a513e3194161eb6bd4c9ae0bcc385172" ns2:_="">
     <xsd:import namespace="b2843789-6ce0-4c67-8bf3-b5ed13cce4b2"/>
@@ -66954,31 +66928,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{680E192F-65F2-4B59-AEA2-95F93556C8D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b2843789-6ce0-4c67-8bf3-b5ed13cce4b2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE8CD45A-A0E8-4060-91AF-9B0DE1D8657A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b2843789-6ce0-4c67-8bf3-b5ed13cce4b2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F1B1FE3-8739-421E-89C5-3584D16D6C47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -66994,4 +66963,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE8CD45A-A0E8-4060-91AF-9B0DE1D8657A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{680E192F-65F2-4B59-AEA2-95F93556C8D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b2843789-6ce0-4c67-8bf3-b5ed13cce4b2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Cercospora_TIME_description.xlsx
+++ b/data/Cercospora_TIME_description.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lsuagctr-my.sharepoint.com/personal/acerutti_agcenter_lsu_edu/Documents/Documents/GitHub/Cercospora_TIME/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="796" documentId="8_{B521CAD1-B04F-41B4-8C4D-BBC1E172B03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BDB7F26-B3D6-4FBB-A82D-FD3E807375E7}"/>
+  <xr:revisionPtr revIDLastSave="835" documentId="8_{B521CAD1-B04F-41B4-8C4D-BBC1E172B03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56BA2FE0-22C1-4EFA-9821-4D0465C98BE6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58E64BEA-56DB-4F46-BCEA-90D1CD645A95}"/>
   </bookViews>
@@ -7557,7 +7557,7 @@
       <c r="L74" t="s">
         <v>252</v>
       </c>
-      <c r="M74" s="14" t="s">
+      <c r="M74" s="8" t="s">
         <v>31</v>
       </c>
       <c r="N74" s="14" t="s">
@@ -7632,7 +7632,7 @@
       <c r="L75" t="s">
         <v>252</v>
       </c>
-      <c r="M75" s="14" t="s">
+      <c r="M75" s="8" t="s">
         <v>33</v>
       </c>
       <c r="N75" s="14" t="s">
@@ -7707,7 +7707,7 @@
       <c r="L76" t="s">
         <v>252</v>
       </c>
-      <c r="M76" s="14" t="s">
+      <c r="M76" s="8" t="s">
         <v>31</v>
       </c>
       <c r="N76" s="14" t="s">
@@ -7782,7 +7782,7 @@
       <c r="L77" t="s">
         <v>252</v>
       </c>
-      <c r="M77" s="14" t="s">
+      <c r="M77" s="8" t="s">
         <v>31</v>
       </c>
       <c r="N77" s="14" t="s">
@@ -7857,7 +7857,7 @@
       <c r="L78" t="s">
         <v>252</v>
       </c>
-      <c r="M78" s="14" t="s">
+      <c r="M78" s="8" t="s">
         <v>31</v>
       </c>
       <c r="N78" s="14" t="s">
@@ -8007,7 +8007,7 @@
       <c r="L80" t="s">
         <v>252</v>
       </c>
-      <c r="M80" s="14" t="s">
+      <c r="M80" s="8" t="s">
         <v>31</v>
       </c>
       <c r="N80" s="14" t="s">
@@ -8082,7 +8082,7 @@
       <c r="L81" t="s">
         <v>252</v>
       </c>
-      <c r="M81" s="14" t="s">
+      <c r="M81" s="8" t="s">
         <v>33</v>
       </c>
       <c r="N81" s="14" t="s">
